--- a/data/raw/lieux_upload.xlsx
+++ b/data/raw/lieux_upload.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,68 +451,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HAD MONTROUGE</t>
+          <t>Collège Haut Mesnil</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FINESS</t>
+          <t>data.education.gouv.fr</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>48.81701908628781</v>
+        <v>48.81396906122965</v>
       </c>
       <c r="E2" t="n">
-        <v>2.323909049582313</v>
+        <v>2.307057910317576</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.817019086287814, 2.323909049582313</t>
+          <t>48.81396906122965, 2.307057910317576</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDJ CMP JOAN RIVIERE</t>
+          <t>Collège Maurice Genevoix</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FINESS</t>
+          <t>data.education.gouv.fr</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>48.81678126890864</v>
+        <v>48.81090067352207</v>
       </c>
       <c r="E3" t="n">
-        <v>2.309520981776612</v>
+        <v>2.325197595739604</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.81678126890864, 2.309520981776612</t>
+          <t>48.81090067352207, 2.325197595739604</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Aristide Briand</t>
+          <t>Collège Robert Doisneau</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -521,26 +521,26 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>48.81485220472397</v>
+        <v>48.82039933804069</v>
       </c>
       <c r="E4" t="n">
-        <v>2.325926798091101</v>
+        <v>2.316845525624895</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.81485220472397, 2.3259267980911007</t>
+          <t>48.820399338040694, 2.3168455256248945</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Buffalo</t>
+          <t>Collège privé Jeanne d'Arc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -549,26 +549,26 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>48.81117732063301</v>
+        <v>48.8187827836916</v>
       </c>
       <c r="E5" t="n">
-        <v>2.319895452935603</v>
+        <v>2.318516023815689</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>48.811177320633014, 2.3198954529356026</t>
+          <t>48.818782783691596, 2.3185160238156888</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique François Rabelais</t>
+          <t>Ecole secondaire privée Groupe Scolaire Yaguel Yaacov</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -577,26 +577,26 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>48.81921194608093</v>
+        <v>48.81987094409272</v>
       </c>
       <c r="E6" t="n">
-        <v>2.321706931688225</v>
+        <v>2.312216280016048</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.81921194608093, 2.321706931688225</t>
+          <t>48.81987094409272, 2.3122162800160475</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Haut-Mesnil</t>
+          <t>Ecole secondaire privée Pardess Hannah</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -605,182 +605,2450 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>48.81464114560588</v>
+        <v>48.81289063370255</v>
       </c>
       <c r="E7" t="n">
-        <v>2.307565117329271</v>
+        <v>2.319416907837911</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>48.81464114560588, 2.3075651173292706</t>
+          <t>48.81289063370255, 2.3194169078379105</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Marcellin Berthelot</t>
+          <t>HAD MONTROUGE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>data.education.gouv.fr</t>
+          <t>FINESS</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>48.81614343118439</v>
+        <v>48.81701908628781</v>
       </c>
       <c r="E8" t="n">
-        <v>2.316528127069811</v>
+        <v>2.323909049582313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>48.816143431184386, 2.3165281270698115</t>
+          <t>48.817019086287814, 2.323909049582313</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Maurice Arnoux</t>
+          <t>HDJ CMP JOAN RIVIERE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>data.education.gouv.fr</t>
+          <t>FINESS</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>48.82034024428792</v>
+        <v>48.81678126890864</v>
       </c>
       <c r="E9" t="n">
-        <v>2.313280613082784</v>
+        <v>2.309520981776612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>48.82034024428792, 2.313280613082784</t>
+          <t>48.81678126890864, 2.309520981776612</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Nicolas Boileau</t>
+          <t>CDS CENTRE MEDICAL MONTROUGE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>Centre de Santé</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>data.education.gouv.fr</t>
+          <t>FINESS</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>48.81150373223819</v>
+        <v>48.81326157748526</v>
       </c>
       <c r="E10" t="n">
-        <v>2.317516291018025</v>
+        <v>2.302174343393972</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>48.81150373223819, 2.317516291018025</t>
+          <t>48.81326157748526, 2.302174343393972</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Commissariat de police de Montrouge</t>
+          <t>CDS DENTAIRE AADT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>commissariat</t>
+          <t>Centre de Santé</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>lannuaire.service-public.fr + géocodage BAN</t>
+          <t>FINESS</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>48.815784</v>
+        <v>48.81607892733119</v>
       </c>
       <c r="E11" t="n">
-        <v>2.31347</v>
+        <v>2.310158107636889</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>48.815784, 2.31347</t>
+          <t>48.81607892733119, 2.3101581076368887</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mairie de Montrouge</t>
+          <t>CDS DENTAIRE ODONTALIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>gare</t>
+          <t>Centre de Santé</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>OpenStreetMap</t>
+          <t>FINESS</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>48.8179643</v>
+        <v>48.81069641347636</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3192501</v>
+        <v>2.31318427643796</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>48.8179643, 2.3192501</t>
+          <t>48.810696413476364, 2.31318427643796</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>CDS HOPSOIN VERDIER</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Centre de Santé</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>48.81611588801121</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.309705474757878</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>48.81611588801121, 2.3097054747578785</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CDS MEDICO DENTAIRE DE MONTROUGE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Centre de Santé</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>48.81163433501998</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.3265975234474</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>48.81163433501998, 2.3265975234473997</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CDS MUNICIPAL MONTROUGE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Centre de Santé</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>48.81717137162057</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.323960189382609</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>48.81717137162057, 2.3239601893826087</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CSS DE MONTROUGE</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Centre de santé sexuelle</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>48.81717137162057</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.323960189382609</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>48.81717137162057, 2.3239601893826087</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CPTS DE MONTROUGE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Communautés professionnelles territoriales de santé (CPTS)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>48.81691104454355</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.31850235201646</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>48.816911044543545, 2.3185023520164605</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ecole primaire Pardess Hannah</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>48.81268773657927</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.320587970099393</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>48.81268773657927, 2.3205879700993934</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ecole primaire privée Jeanne d'Arc</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>48.8187827836916</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.318516023815689</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>48.818782783691596, 2.3185160238156888</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ecole primaire privée Yaguel Yaacov</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>48.81987094409272</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.312216280016048</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>48.81987094409272, 2.3122162800160475</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire publique Aristide Briand</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>48.81474745325436</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.328248729191516</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>48.81474745325436, 2.3282487291915164</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire publique Buffalo</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>48.81150441705952</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2.320162176922167</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>48.81150441705952, 2.3201621769221674</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire publique Nicolas Boileau</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>48.81219093954178</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.31815958805646</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>48.81219093954178, 2.3181595880564605</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire publique Rabelais</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>48.81892809454184</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.322403857155729</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>48.81892809454184, 2.322403857155729</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire publique Renaudel</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>48.81295594973342</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.308231623428387</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>48.81295594973342, 2.3082316234283873</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire d'application Raymond Queneau</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ECOLE ELEMENTAIRE D APPLICATION</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>48.81764028582121</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.32210598895006</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>48.817640285821206, 2.3221059889500597</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique Aristide Briand</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>48.81485220472397</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.325926798091101</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>48.81485220472397, 2.3259267980911007</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique Buffalo</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>48.81117732063301</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.319895452935603</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>48.811177320633014, 2.3198954529356026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique François Rabelais</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>48.81921194608093</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.321706931688225</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>48.81921194608093, 2.321706931688225</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique Haut-Mesnil</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>48.81464114560588</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.307565117329271</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>48.81464114560588, 2.3075651173292706</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique Marcellin Berthelot</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>48.81614343118439</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.316528127069811</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>48.816143431184386, 2.3165281270698115</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique Maurice Arnoux</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>48.82034024428792</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.313280613082784</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>48.82034024428792, 2.313280613082784</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique Nicolas Boileau</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>48.81150373223819</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.317516291018025</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>48.81150373223819, 2.317516291018025</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CAJ JEANY</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Etab.Accueil Non Médicalisé pour personnes handicapées</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>48.81468968430205</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.313963767412307</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>48.81468968430205, 2.3139637674123072</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>FOYER JEANY</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Etab.Accueil Non Médicalisé pour personnes handicapées</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>48.81458699868288</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.313623296786707</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>48.814586998682884, 2.3136232967867074</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>GPE HOSP SAINT-JOSEPH - SITE MONTROUGE</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Etablissement de Soins Pluridisciplinaire</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>48.81717137162057</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.323960189382609</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>48.81717137162057, 2.3239601893826087</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Lycée général et technologique Maurice Genevoix</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>LYCEE ENSEIGNT GENERAL ET TECHNOLOGIQUE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>48.81052663525963</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2.322989622297694</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>48.81052663525963, 2.3229896222976945</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Lycée général et technologique privé Jeanne d'Arc</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>LYCEE ENSEIGNT GENERAL ET TECHNOLOGIQUE</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>48.8187827836916</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2.318516023815689</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>48.818782783691596, 2.3185160238156888</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Ecole 2D degré professionnel privée - Académie d'Art Dentaire</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>LYCEE PROFESSIONNEL</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>48.81271833109989</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2.322810010821757</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>48.81271833109989, 2.322810010821757</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Lycée professionnel Jean Monnet , lycée des métiers de la construction et de la gestion administrative</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>LYCEE PROFESSIONNEL</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>48.81281480460642</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2.305294745262522</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>48.81281480460642, 2.3052947452625223</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>LBM BIO ETHERNALYS SITE MONTROUGE</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Laboratoire de Biologie Médicale</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>48.81895943568072</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2.323021775402693</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>48.81895943568072, 2.3230217754026925</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>LBM BIOGROUP PARIS OUEST SITE BROSSOLE</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Laboratoire de Biologie Médicale</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>48.81157993492282</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2.300365275444528</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>48.81157993492282, 2.3003652754445283</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>LBM BIOGROUP PARIS OUEST SITE MONTROUG</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Laboratoire de Biologie Médicale</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>48.81513504074363</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2.317606311967972</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>48.81513504074363, 2.3176063119679724</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Section d'enseignement général et professionnel adapté du Collège Robert Doisneau</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SECTION ENSEIGNT GEN. ET PROF. ADAPTE</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>48.82039933804069</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2.316845525624895</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>48.820399338040694, 2.3168455256248945</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CCAS/CIAS MONTROUGE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Service de Soins Infirmiers A Domicile (S.S.I.A.D)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>48.81717137162057</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2.323960189382609</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>48.81717137162057, 2.3239601893826087</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CREDIT AGRICOLE CIB</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Services de Prévention et de Santé au Travail (SPST)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>48.8174900983744</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2.315641574050415</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>48.8174900983744, 2.315641574050415</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Aumônerie des Jeunes</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>centre culturel</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>48.8147997</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2.3188716</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>48.8147997, 2.3188716</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Centre pastoral catholique</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>centre culturel</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>48.818019</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2.3184672</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>48.818019, 2.3184672</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Espace Jeunes Saint-Martin</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>centre culturel</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>48.8154176</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2.3096959</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>48.8154176, 2.3096959</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Espace Michel Colucci</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>centre culturel</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>48.8135615</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2.3106063</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>48.8135615, 2.3106063</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Maison des Associations</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>centre culturel</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>48.813683</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2.3267197</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>48.813683, 2.3267197</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Commissariat de police de Montrouge</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>commissariat</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>lannuaire.service-public.fr + géocodage BAN</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>48.815784</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2.31347</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>48.815784, 2.31347</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Mairie de Montrouge</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gare</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>48.8179643</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2.3192501</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>48.8179643, 2.3192501</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Police municipale</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gendarmerie</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>48.8156606</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2.3195764</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>48.8156606, 2.3195764</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Association mosquée de Montrouge</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>48.8125835</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2.3131517</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>48.8125835, 2.3131517</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Centre évangélique international Évidence</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>48.8145108</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2.3172515</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>48.8145108, 2.3172515</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Oratoire Bienheureux Charles de Foucauld</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>48.8147869</v>
+      </c>
+      <c r="E57" t="n">
+        <v>2.3188595</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>48.8147869, 2.3188595</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>lieu de culte sans nom</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>48.8180645</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2.3185015</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>48.8180645, 2.3185015</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Église Protestante Unie</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>48.8176105</v>
+      </c>
+      <c r="E59" t="n">
+        <v>2.3117168</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>48.8176105, 2.3117168</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Église Saint-Jacques-le-Majeur</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>48.8181396</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2.3204543</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>48.8181396, 2.3204543</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Église Saint-Joseph-Saint-Raymond</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>48.8145944</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2.3095679</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>48.8145944, 2.3095679</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Église Saint-Luc</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>48.8108006</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2.3234878</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>48.8108006, 2.3234878</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Église Évangelique de Salem</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>48.810885</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2.3079518</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>48.810885, 2.3079518</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>Mairie - Montrouge</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>mairie</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>api-lannuaire.service-public.fr + geocodage BAN</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D64" t="n">
         <v>48.818819</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E64" t="n">
         <v>2.319869</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>48.818819, 2.319869</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Pharmacie Renard</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>pharmacie</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>48.8160855</v>
+      </c>
+      <c r="E65" t="n">
+        <v>2.3085881</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>48.8160855, 2.3085881</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Pharmacie Tuffier</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>pharmacie</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>48.8112481</v>
+      </c>
+      <c r="E66" t="n">
+        <v>2.3145403</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>48.8112481, 2.3145403</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Pharmacie de Paris</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>pharmacie</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>48.8185287</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2.3225912</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>48.8185287, 2.3225912</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Pharmacie de l'Aquapol</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>pharmacie</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>48.814625</v>
+      </c>
+      <c r="E68" t="n">
+        <v>2.32043</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>48.814625, 2.32043</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Pharmacie de l'Église</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>pharmacie</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>48.8178715</v>
+      </c>
+      <c r="E69" t="n">
+        <v>2.3190587</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>48.8178715, 2.3190587</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Pharmacie du Fort</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>pharmacie</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>48.8119254</v>
+      </c>
+      <c r="E70" t="n">
+        <v>2.3233672</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>48.8119254, 2.3233672</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Pharmacie du Marché</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>pharmacie</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>48.8166678</v>
+      </c>
+      <c r="E71" t="n">
+        <v>2.3212215</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>48.8166678, 2.3212215</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Pharmacie du Parc</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>pharmacie</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>48.8133473</v>
+      </c>
+      <c r="E72" t="n">
+        <v>2.3162607</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>48.8133473, 2.3162607</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Pharmacie du Square</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>pharmacie</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>48.8135808</v>
+      </c>
+      <c r="E73" t="n">
+        <v>2.3070756</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>48.8135808, 2.3070756</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>pharmacieCOS</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>pharmacie</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>48.8163976</v>
+      </c>
+      <c r="E74" t="n">
+        <v>2.3113604</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>48.8163976, 2.3113604</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>La Poste Montrouge-Vache Noire</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>poste</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>48.8123121</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2.3257731</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>48.8123121, 2.3257731</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>La poste Montrouge Verdier</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>poste</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>48.8151689</v>
+      </c>
+      <c r="E76" t="n">
+        <v>2.3185804</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>48.8151689, 2.3185804</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Mail Boxes Etc</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>poste</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>48.8160054</v>
+      </c>
+      <c r="E77" t="n">
+        <v>2.3210609</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>48.8160054, 2.3210609</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Parcel Centre Vinted Go</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>poste</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>48.8132586</v>
+      </c>
+      <c r="E78" t="n">
+        <v>2.3283416</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>48.8132586, 2.3283416</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Relais Poste</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>poste</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>48.8138579</v>
+      </c>
+      <c r="E79" t="n">
+        <v>2.3075651</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>48.8138579, 2.3075651</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>supermarché</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>48.815778</v>
+      </c>
+      <c r="E80" t="n">
+        <v>2.3075339</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>48.815778, 2.3075339</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Auchan Supermarché</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>supermarché</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>48.8109713</v>
+      </c>
+      <c r="E81" t="n">
+        <v>2.3145574</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>48.8109713, 2.3145574</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Auchan Supermarché</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>supermarché</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>48.8136569</v>
+      </c>
+      <c r="E82" t="n">
+        <v>2.3256145</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>48.8136569, 2.3256145</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Bio C' Bon</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>supermarché</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>48.8170361</v>
+      </c>
+      <c r="E83" t="n">
+        <v>2.3190873</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>48.8170361, 2.3190873</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Biocoop</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>supermarché</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>48.8157088</v>
+      </c>
+      <c r="E84" t="n">
+        <v>2.3113921</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>48.8157088, 2.3113921</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Cocci Market</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>supermarché</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>48.8118207</v>
+      </c>
+      <c r="E85" t="n">
+        <v>2.3232721</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>48.8118207, 2.3232721</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>G20</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>supermarché</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>48.8129799</v>
+      </c>
+      <c r="E86" t="n">
+        <v>2.3100235</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>48.8129799, 2.3100235</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Intermarché</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>supermarché</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>48.8135644</v>
+      </c>
+      <c r="E87" t="n">
+        <v>2.303717</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>48.8135644, 2.303717</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Intermarché</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>supermarché</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>48.8139097</v>
+      </c>
+      <c r="E88" t="n">
+        <v>2.3032627</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>48.8139097, 2.3032627</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>La Vie Claire</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>supermarché</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>48.8110839</v>
+      </c>
+      <c r="E89" t="n">
+        <v>2.3138813</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>48.8110839, 2.3138813</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Lidl</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>supermarché</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>48.8101603</v>
+      </c>
+      <c r="E90" t="n">
+        <v>2.3183466</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>48.8101603, 2.3183466</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Monoprix</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>supermarché</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>48.8156483</v>
+      </c>
+      <c r="E91" t="n">
+        <v>2.317653</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>48.8156483, 2.317653</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Naturalia</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>supermarché</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>48.8186785</v>
+      </c>
+      <c r="E92" t="n">
+        <v>2.3239862</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>48.8186785, 2.3239862</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Rapid Market</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>supermarché</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>48.8184872</v>
+      </c>
+      <c r="E93" t="n">
+        <v>2.3258565</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>48.8184872, 2.3258565</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>U Express</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>supermarché</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>48.816795</v>
+      </c>
+      <c r="E94" t="n">
+        <v>2.3216547</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>48.816795, 2.3216547</t>
         </is>
       </c>
     </row>

--- a/data/raw/lieux_upload.xlsx
+++ b/data/raw/lieux_upload.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,68 +451,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HAD MONTROUGE</t>
+          <t>Collège Haut Mesnil</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FINESS</t>
+          <t>data.education.gouv.fr</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>48.81701908628781</v>
+        <v>48.81396906122965</v>
       </c>
       <c r="E2" t="n">
-        <v>2.323909049582313</v>
+        <v>2.307057910317576</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.817019086287814, 2.323909049582313</t>
+          <t>48.81396906122965, 2.307057910317576</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDJ CMP JOAN RIVIERE</t>
+          <t>Collège Maurice Genevoix</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FINESS</t>
+          <t>data.education.gouv.fr</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>48.81678126890864</v>
+        <v>48.81090067352207</v>
       </c>
       <c r="E3" t="n">
-        <v>2.309520981776612</v>
+        <v>2.325197595739604</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.81678126890864, 2.309520981776612</t>
+          <t>48.81090067352207, 2.325197595739604</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Aristide Briand</t>
+          <t>Collège Robert Doisneau</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -521,26 +521,26 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>48.81485220472397</v>
+        <v>48.82039933804069</v>
       </c>
       <c r="E4" t="n">
-        <v>2.325926798091101</v>
+        <v>2.316845525624895</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.81485220472397, 2.3259267980911007</t>
+          <t>48.820399338040694, 2.3168455256248945</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Buffalo</t>
+          <t>Collège privé Jeanne d'Arc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -549,26 +549,26 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>48.81117732063301</v>
+        <v>48.8187827836916</v>
       </c>
       <c r="E5" t="n">
-        <v>2.319895452935603</v>
+        <v>2.318516023815689</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>48.811177320633014, 2.3198954529356026</t>
+          <t>48.818782783691596, 2.3185160238156888</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique François Rabelais</t>
+          <t>Ecole secondaire privée Groupe Scolaire Yaguel Yaacov</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -577,26 +577,26 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>48.81921194608093</v>
+        <v>48.81987094409272</v>
       </c>
       <c r="E6" t="n">
-        <v>2.321706931688225</v>
+        <v>2.312216280016048</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.81921194608093, 2.321706931688225</t>
+          <t>48.81987094409272, 2.3122162800160475</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Haut-Mesnil</t>
+          <t>Ecole secondaire privée Pardess Hannah</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -605,182 +605,1106 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>48.81464114560588</v>
+        <v>48.81289063370255</v>
       </c>
       <c r="E7" t="n">
-        <v>2.307565117329271</v>
+        <v>2.319416907837911</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>48.81464114560588, 2.3075651173292706</t>
+          <t>48.81289063370255, 2.3194169078379105</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Marcellin Berthelot</t>
+          <t>HAD MONTROUGE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>data.education.gouv.fr</t>
+          <t>FINESS</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>48.81614343118439</v>
+        <v>48.81701908628781</v>
       </c>
       <c r="E8" t="n">
-        <v>2.316528127069811</v>
+        <v>2.323909049582313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>48.816143431184386, 2.3165281270698115</t>
+          <t>48.817019086287814, 2.323909049582313</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Maurice Arnoux</t>
+          <t>HDJ CMP JOAN RIVIERE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>data.education.gouv.fr</t>
+          <t>FINESS</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>48.82034024428792</v>
+        <v>48.81678126890864</v>
       </c>
       <c r="E9" t="n">
-        <v>2.313280613082784</v>
+        <v>2.309520981776612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>48.82034024428792, 2.313280613082784</t>
+          <t>48.81678126890864, 2.309520981776612</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Nicolas Boileau</t>
+          <t>CDS CENTRE MEDICAL MONTROUGE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>Centre de Santé</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>data.education.gouv.fr</t>
+          <t>FINESS</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>48.81150373223819</v>
+        <v>48.81326157748526</v>
       </c>
       <c r="E10" t="n">
-        <v>2.317516291018025</v>
+        <v>2.302174343393972</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>48.81150373223819, 2.317516291018025</t>
+          <t>48.81326157748526, 2.302174343393972</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Commissariat de police de Montrouge</t>
+          <t>CDS DENTAIRE AADT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>commissariat</t>
+          <t>Centre de Santé</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>lannuaire.service-public.fr + géocodage BAN</t>
+          <t>FINESS</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>48.815784</v>
+        <v>48.81607892733119</v>
       </c>
       <c r="E11" t="n">
-        <v>2.31347</v>
+        <v>2.310158107636889</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>48.815784, 2.31347</t>
+          <t>48.81607892733119, 2.3101581076368887</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mairie de Montrouge</t>
+          <t>CDS DENTAIRE ODONTALIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>gare</t>
+          <t>Centre de Santé</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>OpenStreetMap</t>
+          <t>FINESS</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>48.8179643</v>
+        <v>48.81069641347636</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3192501</v>
+        <v>2.31318427643796</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>48.8179643, 2.3192501</t>
+          <t>48.810696413476364, 2.31318427643796</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>CDS HOPSOIN VERDIER</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Centre de Santé</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>48.81611588801121</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.309705474757878</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>48.81611588801121, 2.3097054747578785</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CDS MEDICO DENTAIRE DE MONTROUGE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Centre de Santé</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>48.81163433501998</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.3265975234474</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>48.81163433501998, 2.3265975234473997</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CDS MUNICIPAL MONTROUGE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Centre de Santé</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>48.81717137162057</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.323960189382609</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>48.81717137162057, 2.3239601893826087</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CSS DE MONTROUGE</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Centre de santé sexuelle</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>48.81717137162057</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.323960189382609</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>48.81717137162057, 2.3239601893826087</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CPTS DE MONTROUGE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Communautés professionnelles territoriales de santé (CPTS)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>48.81691104454355</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.31850235201646</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>48.816911044543545, 2.3185023520164605</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ecole primaire Pardess Hannah</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>48.81268773657927</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.320587970099393</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>48.81268773657927, 2.3205879700993934</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ecole primaire privée Jeanne d'Arc</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>48.8187827836916</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.318516023815689</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>48.818782783691596, 2.3185160238156888</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ecole primaire privée Yaguel Yaacov</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>48.81987094409272</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.312216280016048</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>48.81987094409272, 2.3122162800160475</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire publique Aristide Briand</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>48.81474745325436</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.328248729191516</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>48.81474745325436, 2.3282487291915164</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire publique Buffalo</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>48.81150441705952</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2.320162176922167</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>48.81150441705952, 2.3201621769221674</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire publique Nicolas Boileau</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>48.81219093954178</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.31815958805646</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>48.81219093954178, 2.3181595880564605</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire publique Rabelais</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>48.81892809454184</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.322403857155729</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>48.81892809454184, 2.322403857155729</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire publique Renaudel</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>48.81295594973342</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.308231623428387</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>48.81295594973342, 2.3082316234283873</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire d'application Raymond Queneau</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ECOLE ELEMENTAIRE D APPLICATION</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>48.81764028582121</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.32210598895006</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>48.817640285821206, 2.3221059889500597</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique Aristide Briand</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>48.81485220472397</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.325926798091101</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>48.81485220472397, 2.3259267980911007</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique Buffalo</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>48.81117732063301</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.319895452935603</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>48.811177320633014, 2.3198954529356026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique François Rabelais</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>48.81921194608093</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.321706931688225</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>48.81921194608093, 2.321706931688225</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique Haut-Mesnil</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>48.81464114560588</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.307565117329271</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>48.81464114560588, 2.3075651173292706</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique Marcellin Berthelot</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>48.81614343118439</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.316528127069811</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>48.816143431184386, 2.3165281270698115</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique Maurice Arnoux</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>48.82034024428792</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.313280613082784</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>48.82034024428792, 2.313280613082784</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique Nicolas Boileau</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>48.81150373223819</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.317516291018025</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>48.81150373223819, 2.317516291018025</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Lycée général et technologique Maurice Genevoix</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>LYCEE ENSEIGNT GENERAL ET TECHNOLOGIQUE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>48.81052663525963</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.322989622297694</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>48.81052663525963, 2.3229896222976945</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Lycée général et technologique privé Jeanne d'Arc</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>LYCEE ENSEIGNT GENERAL ET TECHNOLOGIQUE</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>48.8187827836916</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.318516023815689</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>48.818782783691596, 2.3185160238156888</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Ecole 2D degré professionnel privée - Académie d'Art Dentaire</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>LYCEE PROFESSIONNEL</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>48.81271833109989</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.322810010821757</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>48.81271833109989, 2.322810010821757</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Lycée professionnel Jean Monnet , lycée des métiers de la construction et de la gestion administrative</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>LYCEE PROFESSIONNEL</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>48.81281480460642</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2.305294745262522</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>48.81281480460642, 2.3052947452625223</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Commissariat de police de Montrouge</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>commissariat</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>lannuaire.service-public.fr + géocodage BAN</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>48.815784</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2.31347</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>48.815784, 2.31347</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Mairie de Montrouge</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>gare</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>48.8179643</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2.3192501</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>48.8179643, 2.3192501</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Police municipale</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>gendarmerie</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>48.8156606</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2.3195764</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>48.8156606, 2.3195764</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Mairie - Montrouge</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>mairie</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>api-lannuaire.service-public.fr + geocodage BAN</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D41" t="n">
         <v>48.818819</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E41" t="n">
         <v>2.319869</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>48.818819, 2.319869</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>La Poste Montrouge-Vache Noire</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>poste</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>48.8123121</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2.3257731</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>48.8123121, 2.3257731</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>La poste Montrouge Verdier</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>poste</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>48.8151689</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2.3185804</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>48.8151689, 2.3185804</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Mail Boxes Etc</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>poste</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>48.8160054</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2.3210609</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>48.8160054, 2.3210609</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Parcel Centre Vinted Go</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>poste</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>48.8132586</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2.3283416</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>48.8132586, 2.3283416</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Relais Poste</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>poste</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>48.8138579</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2.3075651</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>48.8138579, 2.3075651</t>
         </is>
       </c>
     </row>

--- a/data/raw/lieux_upload.xlsx
+++ b/data/raw/lieux_upload.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,68 +451,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HAD MONTROUGE</t>
+          <t>Collège Haut Mesnil</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FINESS</t>
+          <t>data.education.gouv.fr</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>48.81701908628781</v>
+        <v>48.81396906122965</v>
       </c>
       <c r="E2" t="n">
-        <v>2.323909049582313</v>
+        <v>2.307057910317576</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.817019086287814, 2.323909049582313</t>
+          <t>48.81396906122965, 2.307057910317576</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDJ CMP JOAN RIVIERE</t>
+          <t>Collège Maurice Genevoix</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FINESS</t>
+          <t>data.education.gouv.fr</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>48.81678126890864</v>
+        <v>48.81090067352207</v>
       </c>
       <c r="E3" t="n">
-        <v>2.309520981776612</v>
+        <v>2.325197595739604</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.81678126890864, 2.309520981776612</t>
+          <t>48.81090067352207, 2.325197595739604</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Aristide Briand</t>
+          <t>Collège Robert Doisneau</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -521,26 +521,26 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>48.81485220472397</v>
+        <v>48.82039933804069</v>
       </c>
       <c r="E4" t="n">
-        <v>2.325926798091101</v>
+        <v>2.316845525624895</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.81485220472397, 2.3259267980911007</t>
+          <t>48.820399338040694, 2.3168455256248945</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Buffalo</t>
+          <t>Collège privé Jeanne d'Arc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -549,26 +549,26 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>48.81117732063301</v>
+        <v>48.8187827836916</v>
       </c>
       <c r="E5" t="n">
-        <v>2.319895452935603</v>
+        <v>2.318516023815689</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>48.811177320633014, 2.3198954529356026</t>
+          <t>48.818782783691596, 2.3185160238156888</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique François Rabelais</t>
+          <t>Ecole secondaire privée Groupe Scolaire Yaguel Yaacov</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -577,26 +577,26 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>48.81921194608093</v>
+        <v>48.81987094409272</v>
       </c>
       <c r="E6" t="n">
-        <v>2.321706931688225</v>
+        <v>2.312216280016048</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.81921194608093, 2.321706931688225</t>
+          <t>48.81987094409272, 2.3122162800160475</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Haut-Mesnil</t>
+          <t>Ecole secondaire privée Pardess Hannah</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -605,180 +605,936 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>48.81464114560588</v>
+        <v>48.81289063370255</v>
       </c>
       <c r="E7" t="n">
-        <v>2.307565117329271</v>
+        <v>2.319416907837911</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>48.81464114560588, 2.3075651173292706</t>
+          <t>48.81289063370255, 2.3194169078379105</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Marcellin Berthelot</t>
+          <t>HAD MONTROUGE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>data.education.gouv.fr</t>
+          <t>FINESS</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>48.81614343118439</v>
+        <v>48.81701908628781</v>
       </c>
       <c r="E8" t="n">
-        <v>2.316528127069811</v>
+        <v>2.323909049582313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>48.816143431184386, 2.3165281270698115</t>
+          <t>48.817019086287814, 2.323909049582313</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Maurice Arnoux</t>
+          <t>HDJ CMP JOAN RIVIERE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>data.education.gouv.fr</t>
+          <t>FINESS</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>48.82034024428792</v>
+        <v>48.81678126890864</v>
       </c>
       <c r="E9" t="n">
-        <v>2.313280613082784</v>
+        <v>2.309520981776612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>48.82034024428792, 2.313280613082784</t>
+          <t>48.81678126890864, 2.309520981776612</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Nicolas Boileau</t>
+          <t>CDS CENTRE MEDICAL MONTROUGE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>Centre de Santé</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>data.education.gouv.fr</t>
+          <t>FINESS</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>48.81150373223819</v>
+        <v>48.81326157748526</v>
       </c>
       <c r="E10" t="n">
-        <v>2.317516291018025</v>
+        <v>2.302174343393972</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>48.81150373223819, 2.317516291018025</t>
+          <t>48.81326157748526, 2.302174343393972</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Commissariat de police de Montrouge</t>
+          <t>CDS DENTAIRE AADT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>commissariat</t>
+          <t>Centre de Santé</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>lannuaire.service-public.fr + géocodage BAN</t>
+          <t>FINESS</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>48.815784</v>
+        <v>48.81607892733119</v>
       </c>
       <c r="E11" t="n">
-        <v>2.31347</v>
+        <v>2.310158107636889</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>48.815784, 2.31347</t>
+          <t>48.81607892733119, 2.3101581076368887</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mairie de Montrouge</t>
+          <t>CDS DENTAIRE ODONTALIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>gare</t>
+          <t>Centre de Santé</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>OpenStreetMap</t>
+          <t>FINESS</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>48.8179643</v>
+        <v>48.81069641347636</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3192501</v>
+        <v>2.31318427643796</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>48.8179643, 2.3192501</t>
+          <t>48.810696413476364, 2.31318427643796</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>CDS HOPSOIN VERDIER</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Centre de Santé</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>48.81611588801121</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.309705474757878</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>48.81611588801121, 2.3097054747578785</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CDS MEDICO DENTAIRE DE MONTROUGE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Centre de Santé</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>48.81163433501998</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.3265975234474</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>48.81163433501998, 2.3265975234473997</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CDS MUNICIPAL MONTROUGE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Centre de Santé</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>48.81717137162057</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.323960189382609</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>48.81717137162057, 2.3239601893826087</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CSS DE MONTROUGE</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Centre de santé sexuelle</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>48.81717137162057</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.323960189382609</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>48.81717137162057, 2.3239601893826087</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CPTS DE MONTROUGE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Communautés professionnelles territoriales de santé (CPTS)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>48.81691104454355</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.31850235201646</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>48.816911044543545, 2.3185023520164605</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ecole primaire Pardess Hannah</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>48.81268773657927</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.320587970099393</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>48.81268773657927, 2.3205879700993934</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ecole primaire privée Jeanne d'Arc</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>48.8187827836916</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.318516023815689</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>48.818782783691596, 2.3185160238156888</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ecole primaire privée Yaguel Yaacov</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>48.81987094409272</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.312216280016048</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>48.81987094409272, 2.3122162800160475</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire publique Aristide Briand</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>48.81474745325436</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.328248729191516</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>48.81474745325436, 2.3282487291915164</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire publique Buffalo</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>48.81150441705952</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2.320162176922167</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>48.81150441705952, 2.3201621769221674</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire publique Nicolas Boileau</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>48.81219093954178</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.31815958805646</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>48.81219093954178, 2.3181595880564605</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire publique Rabelais</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>48.81892809454184</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.322403857155729</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>48.81892809454184, 2.322403857155729</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire publique Renaudel</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>48.81295594973342</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.308231623428387</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>48.81295594973342, 2.3082316234283873</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire d'application Raymond Queneau</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ECOLE ELEMENTAIRE D APPLICATION</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>48.81764028582121</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.32210598895006</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>48.817640285821206, 2.3221059889500597</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique Aristide Briand</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>48.81485220472397</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.325926798091101</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>48.81485220472397, 2.3259267980911007</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique Buffalo</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>48.81117732063301</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.319895452935603</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>48.811177320633014, 2.3198954529356026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique François Rabelais</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>48.81921194608093</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.321706931688225</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>48.81921194608093, 2.321706931688225</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique Haut-Mesnil</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>48.81464114560588</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.307565117329271</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>48.81464114560588, 2.3075651173292706</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique Marcellin Berthelot</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>48.81614343118439</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.316528127069811</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>48.816143431184386, 2.3165281270698115</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique Maurice Arnoux</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>48.82034024428792</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.313280613082784</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>48.82034024428792, 2.313280613082784</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique Nicolas Boileau</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>48.81150373223819</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.317516291018025</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>48.81150373223819, 2.317516291018025</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Lycée général et technologique Maurice Genevoix</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>LYCEE ENSEIGNT GENERAL ET TECHNOLOGIQUE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>48.81052663525963</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.322989622297694</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>48.81052663525963, 2.3229896222976945</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Lycée général et technologique privé Jeanne d'Arc</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>LYCEE ENSEIGNT GENERAL ET TECHNOLOGIQUE</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>48.8187827836916</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.318516023815689</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>48.818782783691596, 2.3185160238156888</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Ecole 2D degré professionnel privée - Académie d'Art Dentaire</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>LYCEE PROFESSIONNEL</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>48.81271833109989</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.322810010821757</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>48.81271833109989, 2.322810010821757</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Lycée professionnel Jean Monnet , lycée des métiers de la construction et de la gestion administrative</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>LYCEE PROFESSIONNEL</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>48.81281480460642</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2.305294745262522</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>48.81281480460642, 2.3052947452625223</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Commissariat de police de Montrouge</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>commissariat</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>lannuaire.service-public.fr + géocodage BAN</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>48.815784</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2.31347</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>48.815784, 2.31347</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Mairie de Montrouge</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>gare</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>48.8179643</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2.3192501</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>48.8179643, 2.3192501</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Mairie - Montrouge</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>mairie</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>api-lannuaire.service-public.fr + geocodage BAN</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D40" t="n">
         <v>48.818819</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E40" t="n">
         <v>2.319869</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>48.818819, 2.319869</t>
         </is>

--- a/data/raw/lieux_upload.xlsx
+++ b/data/raw/lieux_upload.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -731,26 +731,54 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Mairie de Montrouge</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>gare</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>48.8179643</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.3192501</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>48.8179643, 2.3192501</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Mairie - Montrouge</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>mairie</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>api-lannuaire.service-public.fr + geocodage BAN</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D13" t="n">
         <v>48.818819</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E13" t="n">
         <v>2.319869</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>48.818819, 2.319869</t>
         </is>

--- a/data/raw/lieux_upload.xlsx
+++ b/data/raw/lieux_upload.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -731,54 +731,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mairie de Montrouge</t>
+          <t>Mairie - Montrouge</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>gare</t>
+          <t>mairie</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>OpenStreetMap</t>
+          <t>api-lannuaire.service-public.fr + geocodage BAN</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>48.8179643</v>
+        <v>48.818819</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3192501</v>
+        <v>2.319869</v>
       </c>
       <c r="F12" t="inlineStr">
-        <is>
-          <t>48.8179643, 2.3192501</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Mairie - Montrouge</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>mairie</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>api-lannuaire.service-public.fr + geocodage BAN</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>48.818819</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2.319869</v>
-      </c>
-      <c r="F13" t="inlineStr">
         <is>
           <t>48.818819, 2.319869</t>
         </is>

--- a/data/raw/lieux_upload.xlsx
+++ b/data/raw/lieux_upload.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HAD MONTROUGE</t>
+          <t>CHI DES ALPES DU SUD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+          <t>Centre Hospitalier (C.H.)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -465,26 +465,26 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>48.81701908628781</v>
+        <v>44.55615020845936</v>
       </c>
       <c r="E2" t="n">
-        <v>2.323909049582313</v>
+        <v>6.072879289047154</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.817019086287814, 2.323909049582313</t>
+          <t>44.556150208459364, 6.072879289047154</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDJ CMP JOAN RIVIERE</t>
+          <t>CHI DES ALPES DU SUD SITE DE GAP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+          <t>Centre Hospitalier (C.H.)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -493,105 +493,105 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>48.81678126890864</v>
+        <v>44.55639434462401</v>
       </c>
       <c r="E3" t="n">
-        <v>2.309520981776612</v>
+        <v>6.073268072252509</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.81678126890864, 2.309520981776612</t>
+          <t>44.55639434462401, 6.073268072252509</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Aristide Briand</t>
+          <t>HJ PSY GEN HELENE CHAIGNEAU GAP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>Centre Hospitalier (C.H.)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>data.education.gouv.fr</t>
+          <t>FINESS</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>48.81485220472397</v>
+        <v>44.56544028432427</v>
       </c>
       <c r="E4" t="n">
-        <v>2.325926798091101</v>
+        <v>6.083517547653188</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.81485220472397, 2.3259267980911007</t>
+          <t>44.56544028432427, 6.083517547653188</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Buffalo</t>
+          <t>HJ PSY IJ LA DOUCETTE GAP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>Centre Hospitalier (C.H.)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>data.education.gouv.fr</t>
+          <t>FINESS</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>48.81117732063301</v>
+        <v>44.56076438993705</v>
       </c>
       <c r="E5" t="n">
-        <v>2.319895452935603</v>
+        <v>6.082004407137266</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>48.811177320633014, 2.3198954529356026</t>
+          <t>44.56076438993705, 6.082004407137266</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique François Rabelais</t>
+          <t>PSY IJ LE CORTO MALTESE GAP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>Centre Hospitalier (C.H.)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>data.education.gouv.fr</t>
+          <t>FINESS</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>48.81921194608093</v>
+        <v>44.56532201287292</v>
       </c>
       <c r="E6" t="n">
-        <v>2.321706931688225</v>
+        <v>6.092094563216123</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.81921194608093, 2.321706931688225</t>
+          <t>44.56532201287292, 6.092094563216123</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Haut-Mesnil</t>
+          <t>Ecole maternelle Fontreyne</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -605,21 +605,21 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>48.81464114560588</v>
+        <v>44.5469426518528</v>
       </c>
       <c r="E7" t="n">
-        <v>2.307565117329271</v>
+        <v>6.060859487982519</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>48.81464114560588, 2.3075651173292706</t>
+          <t>44.546942651852795, 6.060859487982519</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Marcellin Berthelot</t>
+          <t>Ecole maternelle Le Rochasson</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -633,21 +633,21 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>48.81614343118439</v>
+        <v>44.56782342061283</v>
       </c>
       <c r="E8" t="n">
-        <v>2.316528127069811</v>
+        <v>6.082189638841484</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>48.816143431184386, 2.3165281270698115</t>
+          <t>44.567823420612825, 6.082189638841484</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Maurice Arnoux</t>
+          <t>Ecole maternelle Paul-Emile Victor</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -661,98 +661,14 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>48.82034024428792</v>
+        <v>44.56961473615492</v>
       </c>
       <c r="E9" t="n">
-        <v>2.313280613082784</v>
+        <v>6.088949619671172</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>48.82034024428792, 2.313280613082784</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Ecole maternelle publique Nicolas Boileau</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ECOLE MATERNELLE</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>data.education.gouv.fr</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>48.81150373223819</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2.317516291018025</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>48.81150373223819, 2.317516291018025</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Commissariat de police de Montrouge</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>commissariat</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>lannuaire.service-public.fr + géocodage BAN</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>48.815784</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2.31347</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>48.815784, 2.31347</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Mairie - Montrouge</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>mairie</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>api-lannuaire.service-public.fr + geocodage BAN</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>48.818819</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2.319869</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>48.818819, 2.319869</t>
+          <t>44.56961473615492, 6.088949619671172</t>
         </is>
       </c>
     </row>

--- a/data/raw/lieux_upload.xlsx
+++ b/data/raw/lieux_upload.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CHI DES ALPES DU SUD</t>
+          <t>HAD MONTROUGE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Centre Hospitalier (C.H.)</t>
+          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -465,26 +465,26 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>44.55615020845936</v>
+        <v>48.8170190862878</v>
       </c>
       <c r="E2" t="n">
-        <v>6.072879289047154</v>
+        <v>2.323909049582313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>44.556150208459364, 6.072879289047154</t>
+          <t>48.817019086287814, 2.323909049582313</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CHI DES ALPES DU SUD SITE DE GAP</t>
+          <t>HDJ CMP JOAN RIVIERE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Centre Hospitalier (C.H.)</t>
+          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -493,105 +493,105 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>44.55639434462401</v>
+        <v>48.81678126890864</v>
       </c>
       <c r="E3" t="n">
-        <v>6.073268072252509</v>
+        <v>2.309520981776612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>44.55639434462401, 6.073268072252509</t>
+          <t>48.81678126890864, 2.309520981776612</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HJ PSY GEN HELENE CHAIGNEAU GAP</t>
+          <t>Ecole maternelle publique Aristide Briand</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Centre Hospitalier (C.H.)</t>
+          <t>ECOLE MATERNELLE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FINESS</t>
+          <t>data.education.gouv.fr</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>44.56544028432427</v>
+        <v>48.81485220472397</v>
       </c>
       <c r="E4" t="n">
-        <v>6.083517547653188</v>
+        <v>2.325926798091101</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>44.56544028432427, 6.083517547653188</t>
+          <t>48.81485220472397, 2.3259267980911007</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HJ PSY IJ LA DOUCETTE GAP</t>
+          <t>Ecole maternelle publique Buffalo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Centre Hospitalier (C.H.)</t>
+          <t>ECOLE MATERNELLE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FINESS</t>
+          <t>data.education.gouv.fr</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>44.56076438993705</v>
+        <v>48.81117732063301</v>
       </c>
       <c r="E5" t="n">
-        <v>6.082004407137266</v>
+        <v>2.319895452935603</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>44.56076438993705, 6.082004407137266</t>
+          <t>48.811177320633014, 2.3198954529356026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PSY IJ LE CORTO MALTESE GAP</t>
+          <t>Ecole maternelle publique François Rabelais</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Centre Hospitalier (C.H.)</t>
+          <t>ECOLE MATERNELLE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FINESS</t>
+          <t>data.education.gouv.fr</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>44.56532201287292</v>
+        <v>48.81921194608093</v>
       </c>
       <c r="E6" t="n">
-        <v>6.092094563216123</v>
+        <v>2.321706931688225</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>44.56532201287292, 6.092094563216123</t>
+          <t>48.81921194608093, 2.321706931688225</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ecole maternelle Fontreyne</t>
+          <t>Ecole maternelle publique Haut-Mesnil</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -605,21 +605,21 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>44.5469426518528</v>
+        <v>48.81464114560588</v>
       </c>
       <c r="E7" t="n">
-        <v>6.060859487982519</v>
+        <v>2.307565117329271</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>44.546942651852795, 6.060859487982519</t>
+          <t>48.81464114560588, 2.3075651173292706</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ecole maternelle Le Rochasson</t>
+          <t>Ecole maternelle publique Marcellin Berthelot</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -633,21 +633,21 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>44.56782342061283</v>
+        <v>48.81614343118439</v>
       </c>
       <c r="E8" t="n">
-        <v>6.082189638841484</v>
+        <v>2.316528127069811</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>44.567823420612825, 6.082189638841484</t>
+          <t>48.816143431184386, 2.3165281270698115</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ecole maternelle Paul-Emile Victor</t>
+          <t>Ecole maternelle publique Maurice Arnoux</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -661,14 +661,126 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>44.56961473615492</v>
+        <v>48.82034024428792</v>
       </c>
       <c r="E9" t="n">
-        <v>6.088949619671172</v>
+        <v>2.313280613082784</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>44.56961473615492, 6.088949619671172</t>
+          <t>48.82034024428792, 2.313280613082784</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique Nicolas Boileau</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>48.81150373223819</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.317516291018025</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>48.81150373223819, 2.317516291018025</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Commissariat de police de Montrouge</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>commissariat</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>lannuaire.service-public.fr + géocodage BAN</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>48.815784</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.31347</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>48.815784, 2.31347</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Mairie - Montrouge</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>mairie</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>api-lannuaire.service-public.fr + geocodage BAN</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>48.818819</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.319869</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>48.818819, 2.319869</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Mairie de Montrouge</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>gare</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ajout particulier</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>48.8183751284591</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.3194283120155</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>48.818420, 2.319451</t>
         </is>
       </c>
     </row>

--- a/data/raw/lieux_upload.xlsx
+++ b/data/raw/lieux_upload.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,68 +451,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HAD MONTROUGE</t>
+          <t>Collège Arthur Rimbaud</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FINESS</t>
+          <t>data.education.gouv.fr</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>48.8170190862878</v>
+        <v>49.91181792655942</v>
       </c>
       <c r="E2" t="n">
-        <v>2.323909049582313</v>
+        <v>2.300203571098342</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.817019086287814, 2.323909049582313</t>
+          <t>49.911817926559415, 2.3002035710983417</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDJ CMP JOAN RIVIERE</t>
+          <t>Collège César Franck</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FINESS</t>
+          <t>data.education.gouv.fr</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>48.81678126890864</v>
+        <v>49.91209371964029</v>
       </c>
       <c r="E3" t="n">
-        <v>2.309520981776612</v>
+        <v>2.310004496325389</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.81678126890864, 2.309520981776612</t>
+          <t>49.91209371964029, 2.3100044963253885</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Aristide Briand</t>
+          <t>Collège Edouard Lucas</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -521,26 +521,26 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>48.81485220472397</v>
+        <v>49.89906876441213</v>
       </c>
       <c r="E4" t="n">
-        <v>2.325926798091101</v>
+        <v>2.268325151983548</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.81485220472397, 2.3259267980911007</t>
+          <t>49.89906876441213, 2.2683251519835483</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Buffalo</t>
+          <t>Collège Jean-Marc Laurent</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -549,26 +549,26 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>48.81117732063301</v>
+        <v>49.87082202447391</v>
       </c>
       <c r="E5" t="n">
-        <v>2.319895452935603</v>
+        <v>2.312558572840342</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>48.811177320633014, 2.3198954529356026</t>
+          <t>49.87082202447391, 2.3125585728403424</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique François Rabelais</t>
+          <t>Collège ROSA PARKS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -577,26 +577,26 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>48.81921194608093</v>
+        <v>49.9176396081107</v>
       </c>
       <c r="E6" t="n">
-        <v>2.321706931688225</v>
+        <v>2.253931461784814</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.81921194608093, 2.321706931688225</t>
+          <t>49.9176396081107, 2.253931461784814</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Haut-Mesnil</t>
+          <t>Collège privé La Providence</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -605,26 +605,26 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>48.81464114560588</v>
+        <v>49.87769015871013</v>
       </c>
       <c r="E7" t="n">
-        <v>2.307565117329271</v>
+        <v>2.300528434496211</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>48.81464114560588, 2.3075651173292706</t>
+          <t>49.87769015871013, 2.300528434496211</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Marcellin Berthelot</t>
+          <t>Collège privé La Salle</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -633,26 +633,26 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>48.81614343118439</v>
+        <v>49.88510127629238</v>
       </c>
       <c r="E8" t="n">
-        <v>2.316528127069811</v>
+        <v>2.304852464073719</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>48.816143431184386, 2.3165281270698115</t>
+          <t>49.88510127629238, 2.304852464073719</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Maurice Arnoux</t>
+          <t>Collège privé Saint Martin</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -661,26 +661,26 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>48.82034024428792</v>
+        <v>49.88416229931024</v>
       </c>
       <c r="E9" t="n">
-        <v>2.313280613082784</v>
+        <v>2.294786444492209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>48.82034024428792, 2.313280613082784</t>
+          <t>49.88416229931024, 2.2947864444922095</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Nicolas Boileau</t>
+          <t>Collège privé Saint Riquier</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -689,98 +689,3458 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>48.81150373223819</v>
+        <v>49.8818414692845</v>
       </c>
       <c r="E10" t="n">
-        <v>2.317516291018025</v>
+        <v>2.324301397872868</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>48.81150373223819, 2.317516291018025</t>
+          <t>49.8818414692845, 2.324301397872868</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Commissariat de police de Montrouge</t>
+          <t>Collège privé Sainte Clotilde</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>commissariat</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>lannuaire.service-public.fr + géocodage BAN</t>
+          <t>data.education.gouv.fr</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>48.815784</v>
+        <v>49.89013705079242</v>
       </c>
       <c r="E11" t="n">
-        <v>2.31347</v>
+        <v>2.300203418979625</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>48.815784, 2.31347</t>
+          <t>49.89013705079242, 2.3002034189796245</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mairie - Montrouge</t>
+          <t>Collège privé Sainte-Famille</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>mairie</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>api-lannuaire.service-public.fr + geocodage BAN</t>
+          <t>data.education.gouv.fr</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>48.818819</v>
+        <v>49.88860870384428</v>
       </c>
       <c r="E12" t="n">
-        <v>2.319869</v>
+        <v>2.308052862242716</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>48.818819, 2.319869</t>
+          <t>49.88860870384428, 2.308052862242716</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mairie de Montrouge</t>
+          <t>ANNEXE CHU AMIENS NORD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>Centre Hospitalier Régional (C.H.R.)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>49.9072961632399</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.290168321832249</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>49.9072961632399, 2.290168321832249</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CHU AMIENS IOP</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Centre Hospitalier Régional (C.H.R.)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>49.87522866246843</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.270286494330627</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>49.87522866246843, 2.270286494330627</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CHU AMIENS SAINT VICTOR</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Centre Hospitalier Régional (C.H.R.)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>49.90449227113112</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.316952085461226</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>49.90449227113112, 2.316952085461226</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CHU AMIENS SUD</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Centre Hospitalier Régional (C.H.R.)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>49.88016789605819</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.269522111758189</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>49.88016789605819, 2.269522111758189</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CENTRE D'ADICTOLOGIE SESAME</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>49.8715087794888</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.306909983195418</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>49.8715087794888, 2.306909983195418</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CONSULTATIONS FÉD. INTERSECT. PÉDOPSY</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>49.86894041600619</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.28372559885367</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>49.86894041600619, 2.28372559885367</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ET PUBLIC DE SANTÉ MENTALE DE LA SOMME</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>49.88533720757766</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.287485864756484</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>49.88533720757766, 2.2874858647564844</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>HDJ ADOLESCENTS LE ROMANÉE TCA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>49.86894041600619</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.28372559885367</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>49.86894041600619, 2.28372559885367</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>HDJ DE PÉDOPSYCHIATRIE LA GRANDE OURSE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>49.87104001478404</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.305836308364829</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>49.871040014784036, 2.3058363083648286</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>HDJ LES FOUGÈRES ADULTE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>49.8928099373918</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2.308938704315825</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>49.892809937391796, 2.3089387043158247</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PFT DE PÉDOPSYCHIATRIE</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>49.86894041600619</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.28372559885367</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>49.86894041600619, 2.28372559885367</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SERVICE MÉDICO PSYCHO RÉGIONAL</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>49.90852486200605</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.323886624592804</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>49.90852486200605, 2.323886624592804</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>URGENCES HOSPITALIERES PSYCHIATRIQUES</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>49.87618209019737</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.255730381687263</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>49.87618209019737, 2.2557303816872634</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CENTRE D'OPHTALMOLOGIE AMIENS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Centre de Santé</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>49.89419545224683</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.293269601176206</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>49.89419545224683, 2.293269601176206</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CENTRE DE SANTÉ DENTAIRE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Centre de Santé</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>49.91371079635773</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.303053157080449</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>49.91371079635773, 2.303053157080449</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CENTRE DENTAIRE AMIENS</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Centre de Santé</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>49.87582334470624</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.271633386791054</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>49.87582334470624, 2.271633386791054</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CENTRE DENTAIRE DE L'HOTEL DE VILLE</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Centre de Santé</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>49.8938249152992</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.293975616152359</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>49.8938249152992, 2.2939756161523595</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CS DENTAIRE AMIENS</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Centre de Santé</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>49.89505995562706</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.298151393042139</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>49.89505995562706, 2.2981513930421387</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CS MUTUALITÉ 80&amp;60 AMIENS</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Centre de Santé</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>49.89639636088535</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.293567312918652</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>49.896396360885355, 2.293567312918652</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CSD DENTAL ACTIVE AMIENS</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Centre de Santé</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>49.8921421501128</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.297226468690944</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>49.892142150112804, 2.297226468690944</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CSD DENTEGO AMIENS</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Centre de Santé</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>49.87681499075846</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.281314322387652</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>49.87681499075846, 2.2813143223876517</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CSD FRANÇAIS AMIENS</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Centre de Santé</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>49.89034070739947</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.305833705513182</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>49.89034070739947, 2.305833705513182</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CSD MOLARIS</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Centre de Santé</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>49.89323044994407</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.300268058230203</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>49.89323044994407, 2.3002680582302033</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CSD SÉRÉNITÉ AMIENS</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Centre de Santé</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>49.87830692663409</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.269301294513816</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>49.87830692663409, 2.2693012945138165</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CSI AMIENS</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Centre de Santé</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>49.88157290259863</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2.287466136965149</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>49.881572902598634, 2.2874661369651488</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CSP AMIENS</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Centre de Santé</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>49.89081293738973</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2.304988775838221</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>49.89081293738973, 2.304988775838221</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CPEF CD80 AMIENS LAGRANGE</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Centre de santé sexuelle</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>49.9103630458041</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2.310724848491911</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>49.9103630458041, 2.3107248484919105</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CPEF CD80 AMIENS RIOLAN</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Centre de santé sexuelle</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>49.88897671212135</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2.315982075947491</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>49.88897671212135, 2.3159820759474905</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CPEF UPJV AMIENS</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Centre de santé sexuelle</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>49.87775696649493</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2.267625633700077</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>49.87775696649493, 2.2676256337000766</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SERVICE DE SOINS SNCF</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Centre de soins et de prévention</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>49.88972688186482</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2.311508440238902</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>49.889726881864824, 2.3115084402389017</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CPTS GRAND AMIENS</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Communautés professionnelles territoriales de santé (CPTS)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>49.89228940501495</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2.290217229786362</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>49.89228940501495, 2.290217229786362</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Ecole primaire Albert Schweitzer B</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>49.90994109368216</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2.312520864881257</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>49.90994109368216, 2.3125208648812565</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Ecole primaire André Bernard</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>49.87642364639829</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2.306078638386637</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>49.876423646398294, 2.306078638386637</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Ecole primaire Beauvillé</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>49.90647685552141</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2.318418023998497</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>49.90647685552141, 2.3184180239984973</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Ecole primaire Bords de Somme</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>49.9176396081107</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2.253931461784814</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>49.9176396081107, 2.253931461784814</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Ecole primaire Emile Lesot Groupe A</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>49.90981789101092</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2.298109633290363</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>49.90981789101092, 2.298109633290363</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Ecole primaire Emile Lesot Groupe B</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>49.90981789101092</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2.298109633290363</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>49.90981789101092, 2.298109633290363</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Ecole primaire Faubourg de Beauvais</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>49.88945401084758</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2.28894820275752</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>49.88945401084758, 2.28894820275752</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Ecole primaire Georges Quarante</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>49.91366812526692</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2.256453361916217</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>49.91366812526692, 2.256453361916217</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Ecole primaire JEAN FRANCOIS LESUEUR</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>49.8945781275416</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2.30469271855797</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>49.8945781275416, 2.30469271855797</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Ecole primaire Jules Lefèbvre</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>49.88733884623341</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2.291508322661179</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>49.88733884623341, 2.2915083226611785</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Ecole primaire Les Violettes</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>49.86705236217961</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2.325283881221674</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>49.86705236217961, 2.325283881221674</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Ecole primaire Longpré</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>49.92301183556152</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2.262848492584958</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>49.92301183556152, 2.262848492584958</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Ecole primaire Louise Michel</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>49.91598388864506</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2.24863694695263</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>49.91598388864506, 2.2486369469526304</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Ecole primaire Léon Lamotte</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>49.91544394287633</v>
+      </c>
+      <c r="E57" t="n">
+        <v>2.251289911079103</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>49.91544394287633, 2.251289911079103</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Ecole primaire Petit Saint Jean</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>49.88766602481558</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2.261936780464719</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>49.88766602481558, 2.2619367804647186</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Ecole primaire Pigeonnier</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>49.90992743958513</v>
+      </c>
+      <c r="E59" t="n">
+        <v>2.303284316511292</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>49.909927439585125, 2.3032843165112924</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Ecole primaire RENANCOURT</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>49.89550386395177</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2.261717676649059</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>49.89550386395177, 2.2617176766490594</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Ecole primaire Réaumur</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>49.87361793500266</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2.311147505941082</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>49.873617935002656, 2.3111475059410824</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Ecole primaire Sagebien</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>49.87777941506771</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2.291229555885662</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>49.877779415067714, 2.2912295558856624</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Ecole primaire Saint-Leu</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>49.89784699389323</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2.304646766067795</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>49.89784699389323, 2.304646766067795</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Ecole primaire Saint-Maurice A</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>49.90322477351796</v>
+      </c>
+      <c r="E64" t="n">
+        <v>2.290614440657933</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>49.903224773517955, 2.290614440657933</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Ecole primaire privée Coeur- Immaculé</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>49.87433505366446</v>
+      </c>
+      <c r="E65" t="n">
+        <v>2.329432958322345</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>49.87433505366446, 2.329432958322345</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Ecole primaire privée La Providence</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>49.87769015871013</v>
+      </c>
+      <c r="E66" t="n">
+        <v>2.300528434496211</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>49.87769015871013, 2.300528434496211</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Ecole primaire privée La Salle</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>49.89740336997301</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2.305782089190647</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>49.897403369973006, 2.305782089190647</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Ecole primaire privée Notre-Dame du Bon Conseil</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>49.90706622004279</v>
+      </c>
+      <c r="E68" t="n">
+        <v>2.30644619514448</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>49.907066220042786, 2.3064461951444803</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Ecole primaire privée Saint Jean</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>49.90197595087636</v>
+      </c>
+      <c r="E69" t="n">
+        <v>2.278773330799028</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>49.901975950876356, 2.2787733307990283</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Ecole primaire privée Saint Joseph</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>49.90056132009031</v>
+      </c>
+      <c r="E70" t="n">
+        <v>2.299993629180188</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>49.90056132009031, 2.299993629180188</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Ecole primaire privée Saint Martin</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>49.88416229931024</v>
+      </c>
+      <c r="E71" t="n">
+        <v>2.294786444492209</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>49.88416229931024, 2.2947864444922095</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Ecole primaire privée Sainte Clotilde</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>49.89013705079242</v>
+      </c>
+      <c r="E72" t="n">
+        <v>2.300203418979625</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>49.89013705079242, 2.3002034189796245</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Ecole primaire privée Sainte Thérèse-Saint Acheul</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>49.88312935906152</v>
+      </c>
+      <c r="E73" t="n">
+        <v>2.325371588114465</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>49.88312935906152, 2.3253715881144648</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Ecole primaire privée Sainte-Famille</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>49.88679459407057</v>
+      </c>
+      <c r="E74" t="n">
+        <v>2.308475134187145</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>49.88679459407057, 2.3084751341871446</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Ecole primaire publique Jules Barni</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>49.88493911253086</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2.321232101575239</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>49.88493911253086, 2.321232101575239</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire EDMOND ROSTAND</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>49.87196039479124</v>
+      </c>
+      <c r="E76" t="n">
+        <v>2.319640772117654</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>49.871960394791245, 2.3196407721176535</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire Jules Verne</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>49.90932302187193</v>
+      </c>
+      <c r="E77" t="n">
+        <v>2.260040289503726</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>49.90932302187193, 2.2600402895037264</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire Julia et Rene Lamps</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>49.87764305171174</v>
+      </c>
+      <c r="E78" t="n">
+        <v>2.326360259890513</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>49.87764305171174, 2.326360259890513</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire La Paix</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>49.91133490440381</v>
+      </c>
+      <c r="E79" t="n">
+        <v>2.298685539326949</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>49.91133490440381, 2.2986855393269487</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire Montessori</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>49.86850540931895</v>
+      </c>
+      <c r="E80" t="n">
+        <v>2.31581722743978</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>49.86850540931895, 2.31581722743978</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire Saint-Maurice B</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>49.90376078399813</v>
+      </c>
+      <c r="E81" t="n">
+        <v>2.287780657920504</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>49.90376078399813, 2.2877806579205044</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire Saint-Pierre</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>49.90321804596847</v>
+      </c>
+      <c r="E82" t="n">
+        <v>2.305716846909964</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>49.90321804596847, 2.305716846909964</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire Voltaire</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>49.91185064900793</v>
+      </c>
+      <c r="E83" t="n">
+        <v>2.317917726285111</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>49.91185064900793, 2.3179177262851107</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire chemin des Hayettes</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>49.88168292633534</v>
+      </c>
+      <c r="E84" t="n">
+        <v>2.281853318908577</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>49.88168292633534, 2.281853318908577</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire publique Saint-Roch A</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>49.89508685412714</v>
+      </c>
+      <c r="E85" t="n">
+        <v>2.28680592251686</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>49.895086854127136, 2.28680592251686</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Ecole primaire Bapaume</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ECOLE ELEMENTAIRE D APPLICATION</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>49.88181164258487</v>
+      </c>
+      <c r="E86" t="n">
+        <v>2.317479563159668</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>49.88181164258487, 2.3174795631596683</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Ecole élément. d'application Delpech</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ECOLE ELEMENTAIRE D APPLICATION</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>49.88090165061244</v>
+      </c>
+      <c r="E87" t="n">
+        <v>2.292999116175995</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>49.88090165061244, 2.292999116175995</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire d'application Châteaudun</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ECOLE ELEMENTAIRE D APPLICATION</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>49.88424030674361</v>
+      </c>
+      <c r="E88" t="n">
+        <v>2.281344592727288</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>49.88424030674361, 2.281344592727288</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Ecole maternelle Chemin des Plantes</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>49.88196166719225</v>
+      </c>
+      <c r="E89" t="n">
+        <v>2.275351057055163</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>49.88196166719225, 2.275351057055163</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Ecole maternelle Condorcet</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>49.87619036149712</v>
+      </c>
+      <c r="E90" t="n">
+        <v>2.325869251793215</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>49.876190361497116, 2.3258692517932147</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Ecole maternelle Edmond Rostand</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>49.87182592580217</v>
+      </c>
+      <c r="E91" t="n">
+        <v>2.319692606058518</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>49.87182592580217, 2.319692606058518</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Ecole maternelle Elbeuf</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>49.88950076588476</v>
+      </c>
+      <c r="E92" t="n">
+        <v>2.276252093037333</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>49.88950076588476, 2.276252093037333</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Ecole maternelle Emile Lesot</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>49.90970918172923</v>
+      </c>
+      <c r="E93" t="n">
+        <v>2.300459255037756</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>49.90970918172923, 2.3004592550377563</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Ecole maternelle Gustave Charpentier</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>49.914191335456</v>
+      </c>
+      <c r="E94" t="n">
+        <v>2.304927479492203</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>49.914191335456, 2.3049274794922034</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Ecole maternelle Jacques Prévert</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>49.87723769666867</v>
+      </c>
+      <c r="E95" t="n">
+        <v>2.326489337300373</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>49.877237696668665, 2.3264893373003726</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Ecole maternelle Jean Macé</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>49.88467700593547</v>
+      </c>
+      <c r="E96" t="n">
+        <v>2.311475090227687</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>49.884677005935465, 2.3114750902276873</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Ecole maternelle Jules Verne</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>49.90938372540389</v>
+      </c>
+      <c r="E97" t="n">
+        <v>2.25997681060882</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>49.90938372540389, 2.25997681060882</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Ecole maternelle La Paix</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>49.91133490440381</v>
+      </c>
+      <c r="E98" t="n">
+        <v>2.298685539326949</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>49.91133490440381, 2.2986855393269487</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Ecole maternelle La Pépinière</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>49.90695639288226</v>
+      </c>
+      <c r="E99" t="n">
+        <v>2.282280537598026</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>49.906956392882265, 2.2822805375980257</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Ecole maternelle La Vallée</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>49.89305714995542</v>
+      </c>
+      <c r="E100" t="n">
+        <v>2.312944494833455</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>49.893057149955425, 2.3129444948334554</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Ecole maternelle Le Soleil</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>49.90879696182941</v>
+      </c>
+      <c r="E101" t="n">
+        <v>2.295383327020532</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>49.90879696182941, 2.2953833270205317</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Ecole maternelle Les Verrières</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>49.89341701209143</v>
+      </c>
+      <c r="E102" t="n">
+        <v>2.288538350315694</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>49.893417012091426, 2.288538350315694</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Ecole maternelle Léo Lagrange</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>49.91129407652246</v>
+      </c>
+      <c r="E103" t="n">
+        <v>2.313014552055325</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>49.91129407652246, 2.313014552055325</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Ecole maternelle Michel Ange</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>49.92056519682842</v>
+      </c>
+      <c r="E104" t="n">
+        <v>2.298507083039083</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>49.92056519682842, 2.298507083039083</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Ecole maternelle Saint-Maurice</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>49.90350342605576</v>
+      </c>
+      <c r="E105" t="n">
+        <v>2.28724458200899</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>49.90350342605576, 2.28724458200899</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Ecole maternelle Saint-Pierre</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>49.90321804596847</v>
+      </c>
+      <c r="E106" t="n">
+        <v>2.305716846909964</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>49.90321804596847, 2.305716846909964</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Ecole maternelle Saint-Roch</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>49.89587393400635</v>
+      </c>
+      <c r="E107" t="n">
+        <v>2.287595957137808</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>49.895873934006346, 2.287595957137808</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Ecole maternelle Voltaire</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>49.91185064900793</v>
+      </c>
+      <c r="E108" t="n">
+        <v>2.317917726285111</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>49.91185064900793, 2.3179177262851107</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Ecole maternelle d'application André Chénier</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE D APPLICATION</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>49.87768040939811</v>
+      </c>
+      <c r="E109" t="n">
+        <v>2.288261468411943</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>49.87768040939811, 2.2882614684119433</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Ecole maternelle d'application Chateaudun</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE D APPLICATION</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>49.88427596893234</v>
+      </c>
+      <c r="E110" t="n">
+        <v>2.281298207884328</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>49.884275968932336, 2.281298207884328</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Ecole maternelle d'application Delpech</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE D APPLICATION</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>49.8806023595187</v>
+      </c>
+      <c r="E111" t="n">
+        <v>2.292821137015484</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>49.880602359518704, 2.2928211370154843</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Lycée général Madeleine Michelis</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>LYCEE D ENSEIGNEMENT GENERAL</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>49.88921414281806</v>
+      </c>
+      <c r="E112" t="n">
+        <v>2.302983194763526</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>49.88921414281806, 2.302983194763526</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Lycée d'enseignement technologique Edouard Branly</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>LYCEE D ENSEIGNEMENT TECHNOLOGIQUE</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>49.8791074014261</v>
+      </c>
+      <c r="E113" t="n">
+        <v>2.297171051201226</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>49.8791074014261, 2.2971710512012264</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Lycée d'enseignement technologique Edouard Gand</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>LYCEE D ENSEIGNEMENT TECHNOLOGIQUE</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>49.8791074014261</v>
+      </c>
+      <c r="E114" t="n">
+        <v>2.297171051201226</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>49.8791074014261, 2.2971710512012264</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Lycée d'enseignement général et technologique privé Saint Martin</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>LYCEE ENSEIGNT GENERAL ET TECHNOLOGIQUE</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>49.88416229931024</v>
+      </c>
+      <c r="E115" t="n">
+        <v>2.294786444492209</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>49.88416229931024, 2.2947864444922095</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Lycée d'enseignement général et technologique privé Saint Rémi</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>LYCEE ENSEIGNT GENERAL ET TECHNOLOGIQUE</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>49.89384246381353</v>
+      </c>
+      <c r="E116" t="n">
+        <v>2.298264099390701</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>49.89384246381353, 2.298264099390701</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Lycée général et technologique Jean Baptiste Delambre</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>LYCEE ENSEIGNT GENERAL ET TECHNOLOGIQUE</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>49.91214643033441</v>
+      </c>
+      <c r="E117" t="n">
+        <v>2.322320878461479</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>49.91214643033441, 2.3223208784614786</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Lycée général et technologique Robert de Luzarches</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>LYCEE ENSEIGNT GENERAL ET TECHNOLOGIQUE</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>49.88550485369621</v>
+      </c>
+      <c r="E118" t="n">
+        <v>2.320220701335441</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>49.88550485369621, 2.320220701335441</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Lycée général et technologique privé Sacré-Coeur</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>LYCEE ENSEIGNT GENERAL ET TECHNOLOGIQUE</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>49.89315926784747</v>
+      </c>
+      <c r="E119" t="n">
+        <v>2.305105603573589</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>49.893159267847466, 2.3051056035735886</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Lycée général et technologique privé Sainte-Famille</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>LYCEE ENSEIGNT GENERAL ET TECHNOLOGIQUE</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>49.88860870384428</v>
+      </c>
+      <c r="E120" t="n">
+        <v>2.308052862242716</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>49.88860870384428, 2.308052862242716</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Micro-lycée de l'académie d'amiens</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>LYCEE EXPERIMENTAL</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>49.91214643033441</v>
+      </c>
+      <c r="E121" t="n">
+        <v>2.322320878461479</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>49.91214643033441, 2.3223208784614786</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Lycée polyvalent La Hotoie</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>LYCEE POLYVALENT</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>49.89593223330833</v>
+      </c>
+      <c r="E122" t="n">
+        <v>2.276415333210671</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>49.89593223330833, 2.2764153332106707</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Centre régional de formation aux métiers du football</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>LYCEE PROFESSIONNEL</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>49.89070527271913</v>
+      </c>
+      <c r="E123" t="n">
+        <v>2.26567512269887</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>49.89070527271913, 2.26567512269887</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Ecole du second degré privée hors contrat Ecole Terrade à Amiens</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>LYCEE PROFESSIONNEL</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>49.88933300126198</v>
+      </c>
+      <c r="E124" t="n">
+        <v>2.310475044098005</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>49.88933300126198, 2.3104750440980046</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Lycée professionnel Edouard Gand - Lycée des métiers des services à la personne et aux organisations</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>LYCEE PROFESSIONNEL</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>49.8791074014261</v>
+      </c>
+      <c r="E125" t="n">
+        <v>2.297171051201226</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>49.8791074014261, 2.2971710512012264</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Lycée professionnel Montaigne - Lycée des métiers des mobilités et des énergies nouvelles</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>LYCEE PROFESSIONNEL</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>49.91055117159291</v>
+      </c>
+      <c r="E126" t="n">
+        <v>2.319605807184914</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>49.91055117159291, 2.319605807184914</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Lycée professionnel de l'Acheuléen - Lycée des métiers du bâtiment</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>LYCEE PROFESSIONNEL</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>49.8809083837674</v>
+      </c>
+      <c r="E127" t="n">
+        <v>2.325010285288347</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>49.8809083837674, 2.3250102852883474</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Lycée professionnel privé Sacré-Coeur</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>LYCEE PROFESSIONNEL</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>49.89315926784747</v>
+      </c>
+      <c r="E128" t="n">
+        <v>2.305105603573589</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>49.893159267847466, 2.3051056035735886</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Commissariat de police d'Amiens</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>commissariat</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>lannuaire.service-public.fr + géocodage BAN</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>49.906615</v>
+      </c>
+      <c r="E129" t="n">
+        <v>2.290747</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>49.906615, 2.290747</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Commissariat de police d'Amiens -  Secteur Centre</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>commissariat</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>lannuaire.service-public.fr + géocodage BAN</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>49.889792</v>
+      </c>
+      <c r="E130" t="n">
+        <v>2.302811</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>49.889792, 2.302811</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Amiens</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
           <t>gare</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>ajout particulier</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>48.8183751284591</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2.3194283120155</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>48.818420, 2.319451</t>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>49.8905599</v>
+      </c>
+      <c r="E131" t="n">
+        <v>2.3081986</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>49.8905599, 2.3081986</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Gare Saint-Roch</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>gare</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>49.8932209</v>
+      </c>
+      <c r="E132" t="n">
+        <v>2.2834356</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>49.8932209, 2.2834356</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Mairie - Amiens</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>mairie</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>api-lannuaire.service-public.fr + geocodage BAN</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>49.893238</v>
+      </c>
+      <c r="E133" t="n">
+        <v>2.295394</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>49.893238, 2.295394</t>
         </is>
       </c>
     </row>

--- a/data/raw/lieux_upload.xlsx
+++ b/data/raw/lieux_upload.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GHU APHP UPS SITE RAYMOND POINCARE</t>
+          <t>HAD MONTROUGE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Régional (C.H.R.)</t>
+          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -465,49 +465,49 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>48.83837956877019</v>
+        <v>48.81701908628781</v>
       </c>
       <c r="E2" t="n">
-        <v>2.170731388514487</v>
+        <v>2.323909049582313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.838379568770186, 2.1707313885144868</t>
+          <t>48.817019086287814, 2.323909049582313</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Gaston Ramon</t>
+          <t>HDJ CMP JOAN RIVIERE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>data.education.gouv.fr</t>
+          <t>FINESS</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>48.85208204917271</v>
+        <v>48.81678126890864</v>
       </c>
       <c r="E3" t="n">
-        <v>2.196893815440051</v>
+        <v>2.309520981776612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.85208204917271, 2.1968938154400512</t>
+          <t>48.81678126890864, 2.309520981776612</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Louis Pasteur</t>
+          <t>Ecole maternelle publique Aristide Briand</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -521,21 +521,21 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>48.84575027126838</v>
+        <v>48.81485220472397</v>
       </c>
       <c r="E4" t="n">
-        <v>2.188337056382556</v>
+        <v>2.325926798091101</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.84575027126838, 2.1883370563825557</t>
+          <t>48.81485220472397, 2.3259267980911007</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Saint-Exupéry</t>
+          <t>Ecole maternelle publique Buffalo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -549,70 +549,238 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>48.84305860241203</v>
+        <v>48.81117732063301</v>
       </c>
       <c r="E5" t="n">
-        <v>2.195151111275364</v>
+        <v>2.319895452935603</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>48.84305860241203, 2.195151111275364</t>
+          <t>48.811177320633014, 2.3198954529356026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Garches - Marnes-la-Coquette</t>
+          <t>Ecole maternelle publique François Rabelais</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>gare</t>
+          <t>ECOLE MATERNELLE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OpenStreetMap</t>
+          <t>data.education.gouv.fr</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>48.8382992</v>
+        <v>48.81921194608093</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1871303</v>
+        <v>2.321706931688225</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.8382992, 2.1871303</t>
+          <t>48.81921194608093, 2.321706931688225</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mairie - Garches</t>
+          <t>Ecole maternelle publique Haut-Mesnil</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>48.81464114560588</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.307565117329271</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>48.81464114560588, 2.3075651173292706</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique Marcellin Berthelot</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>48.81614343118439</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.316528127069811</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>48.816143431184386, 2.3165281270698115</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique Maurice Arnoux</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>48.82034024428792</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.313280613082784</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>48.82034024428792, 2.313280613082784</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique Nicolas Boileau</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>48.81150373223819</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.317516291018025</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>48.81150373223819, 2.317516291018025</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Commissariat de police de Montrouge</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>commissariat</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>lannuaire.service-public.fr + géocodage BAN</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>48.815784</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.31347</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>48.815784, 2.31347</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Mairie de Montrouge</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>gare</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>48.8179643</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.3192501</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>48.8179643, 2.3192501</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Mairie - Montrouge</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>mairie</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>api-lannuaire.service-public.fr + geocodage BAN</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>48.843436</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2.187209</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>48.843436, 2.187209</t>
+      <c r="D13" t="n">
+        <v>48.818819</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.319869</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>48.818819, 2.319869</t>
         </is>
       </c>
     </row>

--- a/data/raw/lieux_upload.xlsx
+++ b/data/raw/lieux_upload.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,40 +451,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GHU APHP UPS SITE RAYMOND POINCARE</t>
+          <t>Collège Haut Mesnil</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Régional (C.H.R.)</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FINESS</t>
+          <t>data.education.gouv.fr</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>48.83837956877019</v>
+        <v>48.81396906122965</v>
       </c>
       <c r="E2" t="n">
-        <v>2.170731388514487</v>
+        <v>2.307057910317576</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.838379568770186, 2.1707313885144868</t>
+          <t>48.81396906122965, 2.307057910317576</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Gaston Ramon</t>
+          <t>Collège Maurice Genevoix</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -493,26 +493,26 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>48.85208204917271</v>
+        <v>48.81090067352207</v>
       </c>
       <c r="E3" t="n">
-        <v>2.196893815440051</v>
+        <v>2.325197595739604</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.85208204917271, 2.1968938154400512</t>
+          <t>48.81090067352207, 2.325197595739604</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Louis Pasteur</t>
+          <t>Collège Robert Doisneau</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -521,26 +521,26 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>48.84575027126838</v>
+        <v>48.82039933804069</v>
       </c>
       <c r="E4" t="n">
-        <v>2.188337056382556</v>
+        <v>2.316845525624895</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.84575027126838, 2.1883370563825557</t>
+          <t>48.820399338040694, 2.3168455256248945</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Saint-Exupéry</t>
+          <t>Collège privé Jeanne d'Arc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -549,70 +549,1414 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>48.84305860241203</v>
+        <v>48.8187827836916</v>
       </c>
       <c r="E5" t="n">
-        <v>2.195151111275364</v>
+        <v>2.318516023815689</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>48.84305860241203, 2.195151111275364</t>
+          <t>48.818782783691596, 2.3185160238156888</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Garches - Marnes-la-Coquette</t>
+          <t>Ecole secondaire privée Groupe Scolaire Yaguel Yaacov</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>gare</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OpenStreetMap</t>
+          <t>data.education.gouv.fr</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>48.8382992</v>
+        <v>48.81987094409272</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1871303</v>
+        <v>2.312216280016048</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.8382992, 2.1871303</t>
+          <t>48.81987094409272, 2.3122162800160475</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mairie - Garches</t>
+          <t>Ecole secondaire privée Pardess Hannah</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>COLLEGE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>48.81289063370255</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.319416907837911</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>48.81289063370255, 2.3194169078379105</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HAD MONTROUGE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>48.81701908628781</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.323909049582313</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>48.817019086287814, 2.323909049582313</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HDJ CMP JOAN RIVIERE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>48.81678126890864</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.309520981776612</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>48.81678126890864, 2.309520981776612</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CDS CENTRE MEDICAL MONTROUGE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Centre de Santé</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>48.81326157748526</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.302174343393972</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>48.81326157748526, 2.302174343393972</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CDS DENTAIRE AADT</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Centre de Santé</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>48.81607892733119</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.310158107636889</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>48.81607892733119, 2.3101581076368887</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CDS DENTAIRE ODONTALIA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Centre de Santé</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>48.81069641347636</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.31318427643796</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>48.810696413476364, 2.31318427643796</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CDS HOPSOIN VERDIER</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Centre de Santé</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>48.81611588801121</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.309705474757878</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>48.81611588801121, 2.3097054747578785</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CDS MEDICO DENTAIRE DE MONTROUGE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Centre de Santé</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>48.81163433501998</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.3265975234474</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>48.81163433501998, 2.3265975234473997</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CDS MUNICIPAL MONTROUGE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Centre de Santé</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>48.81717137162057</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.323960189382609</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>48.81717137162057, 2.3239601893826087</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CSS DE MONTROUGE</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Centre de santé sexuelle</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>48.81717137162057</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.323960189382609</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>48.81717137162057, 2.3239601893826087</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CPTS DE MONTROUGE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Communautés professionnelles territoriales de santé (CPTS)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>48.81691104454355</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.31850235201646</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>48.816911044543545, 2.3185023520164605</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ecole primaire Pardess Hannah</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>48.81268773657927</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.320587970099393</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>48.81268773657927, 2.3205879700993934</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ecole primaire privée Jeanne d'Arc</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>48.8187827836916</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.318516023815689</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>48.818782783691596, 2.3185160238156888</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ecole primaire privée Yaguel Yaacov</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>48.81987094409272</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.312216280016048</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>48.81987094409272, 2.3122162800160475</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire publique Aristide Briand</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>48.81474745325436</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.328248729191516</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>48.81474745325436, 2.3282487291915164</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire publique Buffalo</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>48.81150441705952</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2.320162176922167</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>48.81150441705952, 2.3201621769221674</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire publique Nicolas Boileau</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>48.81219093954178</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.31815958805646</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>48.81219093954178, 2.3181595880564605</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire publique Rabelais</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>48.81892809454184</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.322403857155729</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>48.81892809454184, 2.322403857155729</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire publique Renaudel</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>48.81295594973342</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.308231623428387</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>48.81295594973342, 2.3082316234283873</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire d'application Raymond Queneau</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ECOLE ELEMENTAIRE D APPLICATION</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>48.81764028582121</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.32210598895006</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>48.817640285821206, 2.3221059889500597</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique Aristide Briand</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>48.81485220472397</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.325926798091101</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>48.81485220472397, 2.3259267980911007</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique Buffalo</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>48.81117732063301</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.319895452935603</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>48.811177320633014, 2.3198954529356026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique François Rabelais</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>48.81921194608093</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.321706931688225</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>48.81921194608093, 2.321706931688225</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique Haut-Mesnil</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>48.81464114560588</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.307565117329271</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>48.81464114560588, 2.3075651173292706</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique Marcellin Berthelot</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>48.81614343118439</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.316528127069811</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>48.816143431184386, 2.3165281270698115</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique Maurice Arnoux</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>48.82034024428792</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.313280613082784</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>48.82034024428792, 2.313280613082784</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Ecole maternelle publique Nicolas Boileau</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>48.81150373223819</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.317516291018025</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>48.81150373223819, 2.317516291018025</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Lycée général et technologique Maurice Genevoix</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>LYCEE ENSEIGNT GENERAL ET TECHNOLOGIQUE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>48.81052663525963</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.322989622297694</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>48.81052663525963, 2.3229896222976945</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Lycée général et technologique privé Jeanne d'Arc</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>LYCEE ENSEIGNT GENERAL ET TECHNOLOGIQUE</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>48.8187827836916</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.318516023815689</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>48.818782783691596, 2.3185160238156888</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Ecole 2D degré professionnel privée - Académie d'Art Dentaire</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>LYCEE PROFESSIONNEL</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>48.81271833109989</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.322810010821757</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>48.81271833109989, 2.322810010821757</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Lycée professionnel Jean Monnet , lycée des métiers de la construction et de la gestion administrative</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>LYCEE PROFESSIONNEL</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>48.81281480460642</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2.305294745262522</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>48.81281480460642, 2.3052947452625223</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Commissariat de police de Montrouge</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>commissariat</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>lannuaire.service-public.fr + géocodage BAN</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>48.815784</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2.31347</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>48.815784, 2.31347</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Mairie de Montrouge</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>gare</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>48.8179643</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2.3192501</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>48.8179643, 2.3192501</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Police municipale</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>gendarmerie</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>48.8156606</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2.3195764</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>48.8156606, 2.3195764</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Association mosquée de Montrouge</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>48.8125835</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2.3131517</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>48.8125835, 2.3131517</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Centre évangélique international Évidence</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>48.8145108</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2.3172515</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>48.8145108, 2.3172515</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Oratoire Bienheureux Charles de Foucauld</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>48.8147869</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2.3188595</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>48.8147869, 2.3188595</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>lieu de culte sans nom</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>48.8180645</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2.3185015</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>48.8180645, 2.3185015</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Église Protestante Unie</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>48.8176105</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2.3117168</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>48.8176105, 2.3117168</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Église Saint-Jacques-le-Majeur</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>48.8181396</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2.3204543</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>48.8181396, 2.3204543</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Église Saint-Joseph-Saint-Raymond</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>48.8145944</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2.3095679</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>48.8145944, 2.3095679</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Église Saint-Luc</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>48.8108006</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2.3234878</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>48.8108006, 2.3234878</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Église Évangelique de Salem</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>48.810885</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2.3079518</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>48.810885, 2.3079518</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Mairie - Montrouge</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>mairie</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>api-lannuaire.service-public.fr + geocodage BAN</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>48.843436</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2.187209</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>48.843436, 2.187209</t>
+      <c r="D50" t="n">
+        <v>48.818819</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2.319869</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>48.818819, 2.319869</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>La Poste Montrouge-Vache Noire</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>poste</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>48.8123121</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2.3257731</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>48.8123121, 2.3257731</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>La poste Montrouge Verdier</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>poste</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>48.8151689</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2.3185804</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>48.8151689, 2.3185804</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Mail Boxes Etc</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>poste</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>48.8160054</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2.3210609</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>48.8160054, 2.3210609</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Parcel Centre Vinted Go</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>poste</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>48.8132586</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2.3283416</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>48.8132586, 2.3283416</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Relais Poste</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>poste</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>48.8138579</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2.3075651</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>48.8138579, 2.3075651</t>
         </is>
       </c>
     </row>

--- a/data/raw/lieux_upload.xlsx
+++ b/data/raw/lieux_upload.xlsx
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>48.81701908628781</v>
+        <v>48.8170190862878</v>
       </c>
       <c r="E2" t="n">
         <v>2.323909049582313</v>
@@ -731,56 +731,56 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mairie de Montrouge</t>
+          <t>Mairie - Montrouge</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>gare</t>
+          <t>mairie</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>OpenStreetMap</t>
+          <t>api-lannuaire.service-public.fr + geocodage BAN</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>48.8179643</v>
+        <v>48.818819</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3192501</v>
+        <v>2.319869</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>48.8179643, 2.3192501</t>
+          <t>48.818819, 2.319869</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mairie - Montrouge</t>
+          <t>Mairie de Montrouge</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>mairie</t>
+          <t>gare</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>api-lannuaire.service-public.fr + geocodage BAN</t>
+          <t>ajout particulier</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>48.818819</v>
+        <v>48.8183751284591</v>
       </c>
       <c r="E13" t="n">
-        <v>2.319869</v>
+        <v>2.3194283120155</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>48.818819, 2.319869</t>
+          <t>48.818420, 2.319451</t>
         </is>
       </c>
     </row>

--- a/data/raw/lieux_upload.xlsx
+++ b/data/raw/lieux_upload.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>48.8170190862878</v>
+        <v>48.81701908628781</v>
       </c>
       <c r="E2" t="n">
         <v>2.323909049582313</v>
@@ -753,34 +753,6 @@
       <c r="F12" t="inlineStr">
         <is>
           <t>48.818819, 2.319869</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Mairie de Montrouge</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>gare</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>ajout particulier</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>48.8183751284591</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2.3194283120155</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>48.818420, 2.319451</t>
         </is>
       </c>
     </row>

--- a/data/raw/lieux_upload.xlsx
+++ b/data/raw/lieux_upload.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,68 +451,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HAD MONTROUGE</t>
+          <t>Collège Centre</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FINESS</t>
+          <t>data.education.gouv.fr</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>48.81701908628781</v>
+        <v>44.56098044735989</v>
       </c>
       <c r="E2" t="n">
-        <v>2.323909049582313</v>
+        <v>6.074839737462087</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.817019086287814, 2.323909049582313</t>
+          <t>44.56098044735989, 6.074839737462087</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDJ CMP JOAN RIVIERE</t>
+          <t>Collège Mauzan</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FINESS</t>
+          <t>data.education.gouv.fr</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>48.81678126890864</v>
+        <v>44.56586249724505</v>
       </c>
       <c r="E3" t="n">
-        <v>2.309520981776612</v>
+        <v>6.083530538566897</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.81678126890864, 2.309520981776612</t>
+          <t>44.56586249724505, 6.083530538566897</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Aristide Briand</t>
+          <t>Collège de Fontreyne</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -521,26 +521,26 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>48.81485220472397</v>
+        <v>44.53904841153986</v>
       </c>
       <c r="E4" t="n">
-        <v>2.325926798091101</v>
+        <v>6.061104063275448</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.81485220472397, 2.3259267980911007</t>
+          <t>44.53904841153986, 6.061104063275448</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Buffalo</t>
+          <t>Collège privé Saint Joseph</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -549,210 +549,1834 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>48.81117732063301</v>
+        <v>44.5650454297915</v>
       </c>
       <c r="E5" t="n">
-        <v>2.319895452935603</v>
+        <v>6.077619527015007</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>48.811177320633014, 2.3198954529356026</t>
+          <t>44.565045429791496, 6.077619527015007</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique François Rabelais</t>
+          <t>CHI DES ALPES DU SUD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>Centre Hospitalier (C.H.)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>data.education.gouv.fr</t>
+          <t>FINESS</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>48.81921194608093</v>
+        <v>44.55615020845936</v>
       </c>
       <c r="E6" t="n">
-        <v>2.321706931688225</v>
+        <v>6.072879289047154</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.81921194608093, 2.321706931688225</t>
+          <t>44.556150208459364, 6.072879289047154</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Haut-Mesnil</t>
+          <t>CHI DES ALPES DU SUD SITE DE GAP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>Centre Hospitalier (C.H.)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>data.education.gouv.fr</t>
+          <t>FINESS</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>48.81464114560588</v>
+        <v>44.55639434462401</v>
       </c>
       <c r="E7" t="n">
-        <v>2.307565117329271</v>
+        <v>6.073268072252509</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>48.81464114560588, 2.3075651173292706</t>
+          <t>44.55639434462401, 6.073268072252509</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Marcellin Berthelot</t>
+          <t>HJ PSY GEN HELENE CHAIGNEAU GAP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>Centre Hospitalier (C.H.)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>data.education.gouv.fr</t>
+          <t>FINESS</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>48.81614343118439</v>
+        <v>44.56544028432427</v>
       </c>
       <c r="E8" t="n">
-        <v>2.316528127069811</v>
+        <v>6.083517547653188</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>48.816143431184386, 2.3165281270698115</t>
+          <t>44.56544028432427, 6.083517547653188</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Maurice Arnoux</t>
+          <t>HJ PSY IJ LA DOUCETTE GAP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>Centre Hospitalier (C.H.)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>data.education.gouv.fr</t>
+          <t>FINESS</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>48.82034024428792</v>
+        <v>44.56076438993705</v>
       </c>
       <c r="E9" t="n">
-        <v>2.313280613082784</v>
+        <v>6.082004407137266</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>48.82034024428792, 2.313280613082784</t>
+          <t>44.56076438993705, 6.082004407137266</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ecole maternelle publique Nicolas Boileau</t>
+          <t>PSY IJ LE CORTO MALTESE GAP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ECOLE MATERNELLE</t>
+          <t>Centre Hospitalier (C.H.)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>data.education.gouv.fr</t>
+          <t>FINESS</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>48.81150373223819</v>
+        <v>44.56532201287292</v>
       </c>
       <c r="E10" t="n">
-        <v>2.317516291018025</v>
+        <v>6.092094563216123</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>48.81150373223819, 2.317516291018025</t>
+          <t>44.56532201287292, 6.092094563216123</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Commissariat de police de Montrouge</t>
+          <t>CDS DENTAIRE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>commissariat</t>
+          <t>Centre de Santé</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>lannuaire.service-public.fr + géocodage BAN</t>
+          <t>FINESS</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>48.815784</v>
+        <v>44.55549091830345</v>
       </c>
       <c r="E11" t="n">
-        <v>2.31347</v>
+        <v>6.077432345836079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>48.815784, 2.31347</t>
+          <t>44.55549091830345, 6.077432345836079</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mairie - Montrouge</t>
+          <t>CDS HANDICONSULT 05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>mairie</t>
+          <t>Centre de Santé</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>api-lannuaire.service-public.fr + geocodage BAN</t>
+          <t>FINESS</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>48.818819</v>
+        <v>44.5593226410621</v>
       </c>
       <c r="E12" t="n">
-        <v>2.319869</v>
+        <v>6.077719449153656</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>48.818819, 2.319869</t>
+          <t>44.5593226410621, 6.077719449153656</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CPEF GAP</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Centre de santé sexuelle</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>44.55799331528501</v>
+      </c>
+      <c r="E13" t="n">
+        <v>6.077445333557069</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>44.55799331528501, 6.077445333557069</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MAISON DES SOLIDARITES</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Centre de santé sexuelle</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>44.55812260086714</v>
+      </c>
+      <c r="E14" t="n">
+        <v>6.07335463906302</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>44.55812260086714, 6.07335463906302</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CPTS DU GAPENÇAIS</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Communautés professionnelles territoriales de santé (CPTS)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>FINESS</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>44.5560907418779</v>
+      </c>
+      <c r="E15" t="n">
+        <v>6.073461961305674</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>44.5560907418779, 6.073461961305674</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ECOLE PRIMAIRE PRIVEE LA CALANDRETA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>44.52797505242241</v>
+      </c>
+      <c r="E16" t="n">
+        <v>6.035520093811034</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>44.52797505242241, 6.035520093811034</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ECOLE PRIMAIRE PRIVEE SAINTE FAMILLE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>44.54749518948194</v>
+      </c>
+      <c r="E17" t="n">
+        <v>6.063868938052384</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>44.54749518948194, 6.063868938052384</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ecole  élémentaire Paul-Emile Victor</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>44.56958334255835</v>
+      </c>
+      <c r="E18" t="n">
+        <v>6.086560830334214</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>44.56958334255835, 6.086560830334214</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ecole primaire Anselme Gras</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>44.55015979096396</v>
+      </c>
+      <c r="E19" t="n">
+        <v>6.066539668005628</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>44.55015979096396, 6.066539668005628</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ecole primaire Beauregard</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>44.54784276836745</v>
+      </c>
+      <c r="E20" t="n">
+        <v>6.075309483250793</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>44.547842768367445, 6.075309483250793</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ecole primaire Bellevue</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>44.56140168414019</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6.094649541890122</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>44.56140168414019, 6.094649541890122</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ecole primaire Charance</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>44.56981311889504</v>
+      </c>
+      <c r="E22" t="n">
+        <v>6.057060298893344</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>44.56981311889504, 6.057060298893344</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ecole primaire La Gare</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>44.56351963185201</v>
+      </c>
+      <c r="E23" t="n">
+        <v>6.082869436773261</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>44.56351963185201, 6.082869436773261</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ecole primaire La Pépinière</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>44.56152225830701</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6.084160332794233</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>44.56152225830701, 6.084160332794233</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ecole primaire La Tourronde</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>44.51310816091607</v>
+      </c>
+      <c r="E25" t="n">
+        <v>6.056348876995432</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>44.51310816091607, 6.056348876995432</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ecole primaire Lareton</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>44.54597840309285</v>
+      </c>
+      <c r="E26" t="n">
+        <v>6.085618896108727</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>44.54597840309285, 6.085618896108727</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ecole primaire Le Stade</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>44.54777849243243</v>
+      </c>
+      <c r="E27" t="n">
+        <v>6.070369939883916</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>44.54777849243243, 6.070369939883916</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ecole primaire Les Eyssagnières</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>44.55324086066482</v>
+      </c>
+      <c r="E28" t="n">
+        <v>6.055008444278335</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>44.55324086066482, 6.055008444278335</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ecole primaire Pasteur</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>44.55960918286558</v>
+      </c>
+      <c r="E29" t="n">
+        <v>6.078203834796239</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>44.55960918286558, 6.0782038347962395</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ecole primaire Porte-Colombe</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>44.55610213053686</v>
+      </c>
+      <c r="E30" t="n">
+        <v>6.075997747269724</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>44.55610213053686, 6.075997747269724</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ecole primaire Puymaure</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>44.56057370959818</v>
+      </c>
+      <c r="E31" t="n">
+        <v>6.072719467929177</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>44.56057370959818, 6.072719467929177</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Ecole primaire Raymond Chappa</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>44.56281191561366</v>
+      </c>
+      <c r="E32" t="n">
+        <v>6.115938453031851</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>44.56281191561366, 6.115938453031851</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Ecole primaire Romette</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>44.5820893735691</v>
+      </c>
+      <c r="E33" t="n">
+        <v>6.106090164194612</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>44.582089373569104, 6.106090164194612</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ecole primaire privée Saint Coeur</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>44.56102582374877</v>
+      </c>
+      <c r="E34" t="n">
+        <v>6.082419408784127</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>44.56102582374877, 6.082419408784127</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Ecole primaire privée Sainte Jeanne d'Arc</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>44.55914469582665</v>
+      </c>
+      <c r="E35" t="n">
+        <v>6.076735689051866</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>44.55914469582665, 6.0767356890518665</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Ecole élémentaire de Fontreyne</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ECOLE DE NIVEAU ELEMENTAIRE</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>44.54734997853542</v>
+      </c>
+      <c r="E36" t="n">
+        <v>6.060270566141424</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>44.54734997853542, 6.060270566141424</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Ecole maternelle Fontreyne</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>44.5469426518528</v>
+      </c>
+      <c r="E37" t="n">
+        <v>6.060859487982519</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>44.546942651852795, 6.060859487982519</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ecole maternelle Le Rochasson</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>44.56782342061283</v>
+      </c>
+      <c r="E38" t="n">
+        <v>6.082189638841484</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>44.567823420612825, 6.082189638841484</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Ecole maternelle Paul-Emile Victor</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ECOLE MATERNELLE</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>44.56961473615492</v>
+      </c>
+      <c r="E39" t="n">
+        <v>6.088949619671172</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>44.56961473615492, 6.088949619671172</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Lycée général privé Saint Joseph</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>LYCEE D ENSEIGNEMENT GENERAL</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>44.56478394961064</v>
+      </c>
+      <c r="E40" t="n">
+        <v>6.077659453450408</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>44.56478394961064, 6.0776594534504085</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Lycée d'enseignement général et technologique agricole de Gap</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>LYCEE ENSEIGNT GENERAL ET TECHNOLOGIQUE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>44.54066308546264</v>
+      </c>
+      <c r="E41" t="n">
+        <v>6.091216108562817</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>44.54066308546264, 6.091216108562817</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Lycée général et technologique Aristide Briand</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>LYCEE ENSEIGNT GENERAL ET TECHNOLOGIQUE</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>44.56581889584493</v>
+      </c>
+      <c r="E42" t="n">
+        <v>6.083704590092573</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>44.56581889584493, 6.083704590092573</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Lycée général et technologique Dominique Villars</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>LYCEE ENSEIGNT GENERAL ET TECHNOLOGIQUE</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>44.56149108856591</v>
+      </c>
+      <c r="E43" t="n">
+        <v>6.075719422362607</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>44.56149108856591, 6.075719422362607</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Lycée professionnel Paul Héraud - Lycée des métiers de l'habitat et des transports durables</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>LYCEE PROFESSIONNEL</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>44.56869496629943</v>
+      </c>
+      <c r="E44" t="n">
+        <v>6.080789157876749</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>44.56869496629943, 6.080789157876749</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Lycée professionnel Sévigné - Lycée des métiers de la restauration, des services aux entreprises et aux personnes</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>LYCEE PROFESSIONNEL</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>data.education.gouv.fr</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>44.56157076354454</v>
+      </c>
+      <c r="E45" t="n">
+        <v>6.074088095997575</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>44.561570763544545, 6.074088095997575</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>gare</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>44.5638545</v>
+      </c>
+      <c r="E46" t="n">
+        <v>6.0856595</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>44.5638545, 6.0856595</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Police municipale</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gendarmerie</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>44.5555704</v>
+      </c>
+      <c r="E47" t="n">
+        <v>6.0861254</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>44.5555704, 6.0861254</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Police nationale</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>gendarmerie</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>44.560706</v>
+      </c>
+      <c r="E48" t="n">
+        <v>6.080725</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>44.560706, 6.080725</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Cathédrale Saint-Arnoux</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>44.558208</v>
+      </c>
+      <c r="E49" t="n">
+        <v>6.07811</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>44.558208, 6.07811</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Chapelle Notre-Dame</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>44.5578407</v>
+      </c>
+      <c r="E50" t="n">
+        <v>6.0331231</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>44.5578407, 6.0331231</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Chapelle Notre-Dame</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>44.602165</v>
+      </c>
+      <c r="E51" t="n">
+        <v>6.1192075</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>44.602165, 6.1192075</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Chapelle Saint-Jacques-de-la-Tourronde</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>44.5190829</v>
+      </c>
+      <c r="E52" t="n">
+        <v>6.0511027</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>44.5190829, 6.0511027</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Chapelle Saint-Pierre</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>44.5477855</v>
+      </c>
+      <c r="E53" t="n">
+        <v>6.1007715</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>44.5477855, 6.1007715</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Chapelle Sainte-Marie-Madeleine</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>44.6057324</v>
+      </c>
+      <c r="E54" t="n">
+        <v>6.0813911</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>44.6057324, 6.0813911</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Chapelle de Charance</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>44.5707206</v>
+      </c>
+      <c r="E55" t="n">
+        <v>6.0576658</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>44.5707206, 6.0576658</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Chapelle du Saint-Cœur-de-Marie</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>44.56143</v>
+      </c>
+      <c r="E56" t="n">
+        <v>6.0831425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>44.56143, 6.0831425</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Eglise de Sainte Marguerite</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>44.5241709</v>
+      </c>
+      <c r="E57" t="n">
+        <v>6.0731195</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>44.5241709, 6.0731195</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>L'Eglise Evangélique</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>44.5583397</v>
+      </c>
+      <c r="E58" t="n">
+        <v>6.0826758</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>44.5583397, 6.0826758</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Temple Église Réformée</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>44.559761</v>
+      </c>
+      <c r="E59" t="n">
+        <v>6.074655</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>44.559761, 6.074655</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>lieu de culte sans nom</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>44.5349117</v>
+      </c>
+      <c r="E60" t="n">
+        <v>6.0906158</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>44.5349117, 6.0906158</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>lieu de culte sans nom</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>44.6263785</v>
+      </c>
+      <c r="E61" t="n">
+        <v>6.0806656</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>44.6263785, 6.0806656</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Église Notre-Dame d'Espérance</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>44.5681165</v>
+      </c>
+      <c r="E62" t="n">
+        <v>6.0859845</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>44.5681165, 6.0859845</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Église Saint-Pierre</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>44.5809325</v>
+      </c>
+      <c r="E63" t="n">
+        <v>6.1070505</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>44.5809325, 6.1070505</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Église Saint-Roch</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>44.547162</v>
+      </c>
+      <c r="E64" t="n">
+        <v>6.0643225</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>44.547162, 6.0643225</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Église des Cordeliers</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>lieu de culte</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>44.5613975</v>
+      </c>
+      <c r="E65" t="n">
+        <v>6.0827405</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>44.5613975, 6.0827405</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Districolis</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>poste</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>44.5646105</v>
+      </c>
+      <c r="E66" t="n">
+        <v>6.104426</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>44.5646105, 6.104426</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>GAP CORTESE PRESSE</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>poste</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>44.5647058</v>
+      </c>
+      <c r="E67" t="n">
+        <v>6.1044051</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>44.5647058, 6.1044051</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Gap Saint-Roch</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>poste</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>44.5488854</v>
+      </c>
+      <c r="E68" t="n">
+        <v>6.0649941</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>44.5488854, 6.0649941</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Gap Tokoro</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>poste</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>44.569173</v>
+      </c>
+      <c r="E69" t="n">
+        <v>6.1052448</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>44.569173, 6.1052448</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>La Poste</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>poste</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>44.558438</v>
+      </c>
+      <c r="E70" t="n">
+        <v>6.080151</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>44.558438, 6.080151</t>
         </is>
       </c>
     </row>
